--- a/research/traditional_assets/database/data/qatar/qatar_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_real_estate_operations_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07336891760405478</v>
+        <v>0.07333604868645073</v>
       </c>
       <c r="C2">
-        <v>11856.81820688491</v>
+        <v>11758.56045403515</v>
       </c>
       <c r="D2">
-        <v>11820.71820688491</v>
+        <v>11834.24745403514</v>
       </c>
       <c r="E2">
-        <v>-3484.6</v>
+        <v>-3372.813</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>111.787</v>
       </c>
       <c r="G2">
         <v>36.1</v>
@@ -1451,28 +1451,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.6228861</v>
       </c>
       <c r="N2">
-        <v>597.8233333333334</v>
+        <v>592.2004472333334</v>
       </c>
       <c r="O2">
-        <v>59.78233333333334</v>
+        <v>59.22004472333334</v>
       </c>
       <c r="P2">
-        <v>538.0410000000001</v>
+        <v>532.9804025100001</v>
       </c>
       <c r="Q2">
-        <v>544.051</v>
+        <v>538.9904025100001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07336891760405478</v>
+        <v>0.07361954412772802</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.557605483217797</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>106.3196591041269</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07333604868645073</v>
+        <v>0.07330317976884669</v>
       </c>
       <c r="C3">
-        <v>11758.56045403515</v>
+        <v>11660.3337061145</v>
       </c>
       <c r="D3">
-        <v>11834.24745403514</v>
+        <v>11847.8077061145</v>
       </c>
       <c r="E3">
-        <v>-3372.813</v>
+        <v>-3261.026</v>
       </c>
       <c r="F3">
-        <v>111.787</v>
+        <v>223.574</v>
       </c>
       <c r="G3">
         <v>36.1</v>
@@ -1533,28 +1533,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M3">
-        <v>5.6228861</v>
+        <v>11.2457722</v>
       </c>
       <c r="N3">
-        <v>592.2004472333334</v>
+        <v>586.5775611333333</v>
       </c>
       <c r="O3">
-        <v>59.22004472333334</v>
+        <v>58.65775611333333</v>
       </c>
       <c r="P3">
-        <v>532.9804025100001</v>
+        <v>527.91980502</v>
       </c>
       <c r="Q3">
-        <v>538.9904025100001</v>
+        <v>533.92980502</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07361954412772802</v>
+        <v>0.07387528547841499</v>
       </c>
       <c r="T3">
-        <v>0.557605483217797</v>
+        <v>0.5627314758930847</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>106.3196591041269</v>
+        <v>53.15982955206343</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07330317976884669</v>
+        <v>0.07327031085124262</v>
       </c>
       <c r="C4">
-        <v>11660.3337061145</v>
+        <v>11562.1380698261</v>
       </c>
       <c r="D4">
-        <v>11847.8077061145</v>
+        <v>11861.3990698261</v>
       </c>
       <c r="E4">
-        <v>-3261.026</v>
+        <v>-3149.239</v>
       </c>
       <c r="F4">
-        <v>223.574</v>
+        <v>335.361</v>
       </c>
       <c r="G4">
         <v>36.1</v>
@@ -1615,28 +1615,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M4">
-        <v>11.2457722</v>
+        <v>16.8686583</v>
       </c>
       <c r="N4">
-        <v>586.5775611333333</v>
+        <v>580.9546750333334</v>
       </c>
       <c r="O4">
-        <v>58.65775611333333</v>
+        <v>58.09546750333334</v>
       </c>
       <c r="P4">
-        <v>527.91980502</v>
+        <v>522.85920753</v>
       </c>
       <c r="Q4">
-        <v>533.92980502</v>
+        <v>528.86920753</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07387528547841499</v>
+        <v>0.07413629984664188</v>
       </c>
       <c r="T4">
-        <v>0.5627314758930847</v>
+        <v>0.5679631591389969</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>53.15982955206343</v>
+        <v>35.43988636804229</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07327031085124262</v>
+        <v>0.07323744193363857</v>
       </c>
       <c r="C5">
-        <v>11562.1380698261</v>
+        <v>11463.97365236321</v>
       </c>
       <c r="D5">
-        <v>11861.3990698261</v>
+        <v>11875.02165236321</v>
       </c>
       <c r="E5">
-        <v>-3149.239</v>
+        <v>-3037.452</v>
       </c>
       <c r="F5">
-        <v>335.361</v>
+        <v>447.148</v>
       </c>
       <c r="G5">
         <v>36.1</v>
@@ -1697,28 +1697,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M5">
-        <v>16.8686583</v>
+        <v>22.4915444</v>
       </c>
       <c r="N5">
-        <v>580.9546750333334</v>
+        <v>575.3317889333334</v>
       </c>
       <c r="O5">
-        <v>58.09546750333334</v>
+        <v>57.53317889333334</v>
       </c>
       <c r="P5">
-        <v>522.85920753</v>
+        <v>517.7986100400001</v>
       </c>
       <c r="Q5">
-        <v>528.86920753</v>
+        <v>523.8086100400001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07413629984664188</v>
+        <v>0.07440275201420685</v>
       </c>
       <c r="T5">
-        <v>0.5679631591389969</v>
+        <v>0.5733038357858656</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>35.43988636804229</v>
+        <v>26.57991477603172</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07323744193363857</v>
+        <v>0.0732045730160345</v>
       </c>
       <c r="C6">
-        <v>11463.97365236321</v>
+        <v>11365.84056141213</v>
       </c>
       <c r="D6">
-        <v>11875.02165236321</v>
+        <v>11888.67556141212</v>
       </c>
       <c r="E6">
-        <v>-3037.452</v>
+        <v>-2925.665</v>
       </c>
       <c r="F6">
-        <v>447.148</v>
+        <v>558.9350000000001</v>
       </c>
       <c r="G6">
         <v>36.1</v>
@@ -1779,28 +1779,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M6">
-        <v>22.4915444</v>
+        <v>28.1144305</v>
       </c>
       <c r="N6">
-        <v>575.3317889333334</v>
+        <v>569.7089028333334</v>
       </c>
       <c r="O6">
-        <v>57.53317889333334</v>
+        <v>56.97089028333334</v>
       </c>
       <c r="P6">
-        <v>517.7986100400001</v>
+        <v>512.73801255</v>
       </c>
       <c r="Q6">
-        <v>523.8086100400001</v>
+        <v>518.74801255</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07440275201420685</v>
+        <v>0.07467481370108896</v>
       </c>
       <c r="T6">
-        <v>0.5733038357858656</v>
+        <v>0.5787569477305631</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>26.57991477603172</v>
+        <v>21.26393182082537</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0732045730160345</v>
+        <v>0.07317170409843046</v>
       </c>
       <c r="C7">
-        <v>11365.84056141213</v>
+        <v>11267.73890515496</v>
       </c>
       <c r="D7">
-        <v>11888.67556141212</v>
+        <v>11902.36090515496</v>
       </c>
       <c r="E7">
-        <v>-2925.665</v>
+        <v>-2813.878</v>
       </c>
       <c r="F7">
-        <v>558.9350000000001</v>
+        <v>670.7220000000001</v>
       </c>
       <c r="G7">
         <v>36.1</v>
@@ -1861,28 +1861,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M7">
-        <v>28.1144305</v>
+        <v>33.7373166</v>
       </c>
       <c r="N7">
-        <v>569.7089028333334</v>
+        <v>564.0860167333334</v>
       </c>
       <c r="O7">
-        <v>56.97089028333334</v>
+        <v>56.40860167333334</v>
       </c>
       <c r="P7">
-        <v>512.73801255</v>
+        <v>507.67741506</v>
       </c>
       <c r="Q7">
-        <v>518.74801255</v>
+        <v>513.68741506</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07467481370108896</v>
+        <v>0.07495266393450049</v>
       </c>
       <c r="T7">
-        <v>0.5787569477305631</v>
+        <v>0.5843260833336585</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>21.26393182082537</v>
+        <v>17.71994318402114</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07317170409843046</v>
+        <v>0.07313883518082641</v>
       </c>
       <c r="C8">
-        <v>11267.73890515496</v>
+        <v>11169.66879227256</v>
       </c>
       <c r="D8">
-        <v>11902.36090515496</v>
+        <v>11916.07779227256</v>
       </c>
       <c r="E8">
-        <v>-2813.878</v>
+        <v>-2702.091</v>
       </c>
       <c r="F8">
-        <v>670.722</v>
+        <v>782.509</v>
       </c>
       <c r="G8">
         <v>36.1</v>
@@ -1943,28 +1943,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M8">
-        <v>33.7373166</v>
+        <v>39.3602027</v>
       </c>
       <c r="N8">
-        <v>564.0860167333334</v>
+        <v>558.4631306333333</v>
       </c>
       <c r="O8">
-        <v>56.40860167333334</v>
+        <v>55.84631306333333</v>
       </c>
       <c r="P8">
-        <v>507.67741506</v>
+        <v>502.61681757</v>
       </c>
       <c r="Q8">
-        <v>513.68741506</v>
+        <v>508.62681757</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07495266393450049</v>
+        <v>0.07523648944174882</v>
       </c>
       <c r="T8">
-        <v>0.5843260833336585</v>
+        <v>0.5900149852938096</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.71994318402114</v>
+        <v>15.18852272916098</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07313883518082641</v>
+        <v>0.07310596626322236</v>
       </c>
       <c r="C9">
-        <v>11169.66879227256</v>
+        <v>11071.63033194733</v>
       </c>
       <c r="D9">
-        <v>11916.07779227256</v>
+        <v>11929.82633194733</v>
       </c>
       <c r="E9">
-        <v>-2702.091</v>
+        <v>-2590.304</v>
       </c>
       <c r="F9">
-        <v>782.5090000000001</v>
+        <v>894.296</v>
       </c>
       <c r="G9">
         <v>36.1</v>
@@ -2025,28 +2025,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M9">
-        <v>39.3602027</v>
+        <v>44.9830888</v>
       </c>
       <c r="N9">
-        <v>558.4631306333333</v>
+        <v>552.8402445333334</v>
       </c>
       <c r="O9">
-        <v>55.84631306333333</v>
+        <v>55.28402445333334</v>
       </c>
       <c r="P9">
-        <v>502.61681757</v>
+        <v>497.55622008</v>
       </c>
       <c r="Q9">
-        <v>508.62681757</v>
+        <v>503.56622008</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07523648944174882</v>
+        <v>0.07552648506871995</v>
       </c>
       <c r="T9">
-        <v>0.5900149852938097</v>
+        <v>0.5958275590357032</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.18852272916098</v>
+        <v>13.28995738801586</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07310596626322236</v>
+        <v>0.0730730973456183</v>
       </c>
       <c r="C10">
-        <v>11071.63033194733</v>
+        <v>10973.62363386613</v>
       </c>
       <c r="D10">
-        <v>11929.82633194733</v>
+        <v>11943.60663386613</v>
       </c>
       <c r="E10">
-        <v>-2590.304</v>
+        <v>-2478.517</v>
       </c>
       <c r="F10">
-        <v>894.296</v>
+        <v>1006.083</v>
       </c>
       <c r="G10">
         <v>36.1</v>
@@ -2107,28 +2107,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M10">
-        <v>44.9830888</v>
+        <v>50.6059749</v>
       </c>
       <c r="N10">
-        <v>552.8402445333334</v>
+        <v>547.2173584333334</v>
       </c>
       <c r="O10">
-        <v>55.28402445333334</v>
+        <v>54.72173584333334</v>
       </c>
       <c r="P10">
-        <v>497.55622008</v>
+        <v>492.49562259</v>
       </c>
       <c r="Q10">
-        <v>503.56622008</v>
+        <v>498.50562259</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07552648506871995</v>
+        <v>0.07582285422595417</v>
       </c>
       <c r="T10">
-        <v>0.5958275590357032</v>
+        <v>0.6017678816510449</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>13.28995738801586</v>
+        <v>11.8132954560141</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0730730973456183</v>
+        <v>0.07304022842801425</v>
       </c>
       <c r="C11">
-        <v>10973.62363386613</v>
+        <v>10875.64880822325</v>
       </c>
       <c r="D11">
-        <v>11943.60663386613</v>
+        <v>11957.41880822325</v>
       </c>
       <c r="E11">
-        <v>-2478.517</v>
+        <v>-2366.73</v>
       </c>
       <c r="F11">
-        <v>1006.083</v>
+        <v>1117.87</v>
       </c>
       <c r="G11">
         <v>36.1</v>
@@ -2189,28 +2189,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M11">
-        <v>50.6059749</v>
+        <v>56.22886099999999</v>
       </c>
       <c r="N11">
-        <v>547.2173584333334</v>
+        <v>541.5944723333334</v>
       </c>
       <c r="O11">
-        <v>54.72173584333334</v>
+        <v>54.15944723333335</v>
       </c>
       <c r="P11">
-        <v>492.49562259</v>
+        <v>487.4350251000001</v>
       </c>
       <c r="Q11">
-        <v>498.50562259</v>
+        <v>493.4450251000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07582285422595417</v>
+        <v>0.07612580936446027</v>
       </c>
       <c r="T11">
-        <v>0.6017678816510449</v>
+        <v>0.6078402114356166</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.8132954560141</v>
+        <v>10.63196591041269</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07304022842801425</v>
+        <v>0.07300735951041019</v>
       </c>
       <c r="C12">
-        <v>10875.64880822325</v>
+        <v>10777.70596572326</v>
       </c>
       <c r="D12">
-        <v>11957.41880822325</v>
+        <v>11971.26296572326</v>
       </c>
       <c r="E12">
-        <v>-2366.73</v>
+        <v>-2254.943</v>
       </c>
       <c r="F12">
-        <v>1117.87</v>
+        <v>1229.657</v>
       </c>
       <c r="G12">
         <v>36.1</v>
@@ -2271,28 +2271,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M12">
-        <v>56.228861</v>
+        <v>61.8517471</v>
       </c>
       <c r="N12">
-        <v>541.5944723333333</v>
+        <v>535.9715862333334</v>
       </c>
       <c r="O12">
-        <v>54.15944723333334</v>
+        <v>53.59715862333334</v>
       </c>
       <c r="P12">
-        <v>487.4350251</v>
+        <v>482.37442761</v>
       </c>
       <c r="Q12">
-        <v>493.4450251</v>
+        <v>488.38442761</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07612580936446027</v>
+        <v>0.07643557248360695</v>
       </c>
       <c r="T12">
-        <v>0.6078402114356166</v>
+        <v>0.6140489980692796</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.63196591041268</v>
+        <v>9.665423554920624</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07300735951041019</v>
+        <v>0.07297449059280614</v>
       </c>
       <c r="C13">
-        <v>10777.70596572326</v>
+        <v>10679.79521758405</v>
       </c>
       <c r="D13">
-        <v>11971.26296572326</v>
+        <v>11985.13921758405</v>
       </c>
       <c r="E13">
-        <v>-2254.943</v>
+        <v>-2143.156</v>
       </c>
       <c r="F13">
-        <v>1229.657</v>
+        <v>1341.444</v>
       </c>
       <c r="G13">
         <v>36.1</v>
@@ -2353,28 +2353,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M13">
-        <v>61.8517471</v>
+        <v>67.4746332</v>
       </c>
       <c r="N13">
-        <v>535.9715862333334</v>
+        <v>530.3487001333334</v>
       </c>
       <c r="O13">
-        <v>53.59715862333334</v>
+        <v>53.03487001333335</v>
       </c>
       <c r="P13">
-        <v>482.37442761</v>
+        <v>477.31383012</v>
       </c>
       <c r="Q13">
-        <v>488.38442761</v>
+        <v>483.32383012</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07643557248360695</v>
+        <v>0.07675237567364333</v>
       </c>
       <c r="T13">
-        <v>0.6140489980692796</v>
+        <v>0.6203988934900715</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.665423554920624</v>
+        <v>8.859971592010572</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07297449059280614</v>
+        <v>0.07311712167520207</v>
       </c>
       <c r="C14">
-        <v>10679.79521758405</v>
+        <v>10508.0256473821</v>
       </c>
       <c r="D14">
-        <v>11985.13921758405</v>
+        <v>11925.1566473821</v>
       </c>
       <c r="E14">
-        <v>-2143.156</v>
+        <v>-2031.369</v>
       </c>
       <c r="F14">
-        <v>1341.444</v>
+        <v>1453.231</v>
       </c>
       <c r="G14">
         <v>36.1</v>
@@ -2435,45 +2435,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M14">
-        <v>67.4746332</v>
+        <v>75.27736580000001</v>
       </c>
       <c r="N14">
-        <v>530.3487001333334</v>
+        <v>522.5459675333334</v>
       </c>
       <c r="O14">
-        <v>53.03487001333335</v>
+        <v>52.25459675333335</v>
       </c>
       <c r="P14">
-        <v>477.31383012</v>
+        <v>470.2913707800001</v>
       </c>
       <c r="Q14">
-        <v>483.32383012</v>
+        <v>476.3013707800001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07675237567364333</v>
+        <v>0.07707646169563456</v>
       </c>
       <c r="T14">
-        <v>0.6203988934900715</v>
+        <v>0.6268947635182377</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.859971592010572</v>
+        <v>7.941608038220346</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07311712167520207</v>
+        <v>0.07309775275759801</v>
       </c>
       <c r="C15">
-        <v>10508.0256473821</v>
+        <v>10404.34886512807</v>
       </c>
       <c r="D15">
-        <v>11925.1566473821</v>
+        <v>11933.26686512807</v>
       </c>
       <c r="E15">
-        <v>-2031.369</v>
+        <v>-1919.582</v>
       </c>
       <c r="F15">
-        <v>1453.231</v>
+        <v>1565.018</v>
       </c>
       <c r="G15">
         <v>36.1</v>
@@ -2517,28 +2517,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M15">
-        <v>75.27736580000001</v>
+        <v>81.06793240000002</v>
       </c>
       <c r="N15">
-        <v>522.5459675333334</v>
+        <v>516.7554009333334</v>
       </c>
       <c r="O15">
-        <v>52.25459675333335</v>
+        <v>51.67554009333334</v>
       </c>
       <c r="P15">
-        <v>470.2913707800001</v>
+        <v>465.07986084</v>
       </c>
       <c r="Q15">
-        <v>476.3013707800001</v>
+        <v>471.08986084</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07707646169563456</v>
+        <v>0.07740808460185816</v>
       </c>
       <c r="T15">
-        <v>0.6268947635182377</v>
+        <v>0.6335417002912451</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.941608038220346</v>
+        <v>7.374350321204606</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07309775275759801</v>
+        <v>0.07307838383999397</v>
       </c>
       <c r="C16">
-        <v>10404.34886512807</v>
+        <v>10300.68312178914</v>
       </c>
       <c r="D16">
-        <v>11933.26686512807</v>
+        <v>11941.38812178914</v>
       </c>
       <c r="E16">
-        <v>-1919.582</v>
+        <v>-1807.795</v>
       </c>
       <c r="F16">
-        <v>1565.018</v>
+        <v>1676.805</v>
       </c>
       <c r="G16">
         <v>36.1</v>
@@ -2599,28 +2599,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M16">
-        <v>81.06793240000002</v>
+        <v>86.85849900000001</v>
       </c>
       <c r="N16">
-        <v>516.7554009333334</v>
+        <v>510.9648343333334</v>
       </c>
       <c r="O16">
-        <v>51.67554009333334</v>
+        <v>51.09648343333334</v>
       </c>
       <c r="P16">
-        <v>465.07986084</v>
+        <v>459.8683509000001</v>
       </c>
       <c r="Q16">
-        <v>471.08986084</v>
+        <v>465.8783509</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07740808460185816</v>
+        <v>0.07774751039999291</v>
       </c>
       <c r="T16">
-        <v>0.6335417002912451</v>
+        <v>0.6403450355765586</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.374350321204606</v>
+        <v>6.882726966457633</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07307838383999397</v>
+        <v>0.07330381492238991</v>
       </c>
       <c r="C17">
-        <v>10300.68312178914</v>
+        <v>10095.05337559459</v>
       </c>
       <c r="D17">
-        <v>11941.38812178914</v>
+        <v>11847.54537559459</v>
       </c>
       <c r="E17">
-        <v>-1807.795</v>
+        <v>-1696.008</v>
       </c>
       <c r="F17">
-        <v>1676.805</v>
+        <v>1788.592</v>
       </c>
       <c r="G17">
         <v>36.1</v>
@@ -2681,45 +2681,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M17">
-        <v>86.85849899999999</v>
+        <v>95.689672</v>
       </c>
       <c r="N17">
-        <v>510.9648343333334</v>
+        <v>502.1336613333334</v>
       </c>
       <c r="O17">
-        <v>51.09648343333334</v>
+        <v>50.21336613333334</v>
       </c>
       <c r="P17">
-        <v>459.8683509000001</v>
+        <v>451.9202952000001</v>
       </c>
       <c r="Q17">
-        <v>465.8783509</v>
+        <v>457.9302952</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07774751039999291</v>
+        <v>0.07809501776474989</v>
       </c>
       <c r="T17">
-        <v>0.6403450355765586</v>
+        <v>0.647310355035332</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.1</v>
       </c>
       <c r="W17">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.882726966457634</v>
+        <v>6.247522024459792</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07330381492238991</v>
+        <v>0.07329974600478587</v>
       </c>
       <c r="C18">
-        <v>10095.05337559459</v>
+        <v>9984.947117315207</v>
       </c>
       <c r="D18">
-        <v>11847.54537559459</v>
+        <v>11849.22611731521</v>
       </c>
       <c r="E18">
-        <v>-1696.008</v>
+        <v>-1584.221</v>
       </c>
       <c r="F18">
-        <v>1788.592</v>
+        <v>1900.379</v>
       </c>
       <c r="G18">
         <v>36.1</v>
@@ -2763,28 +2763,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M18">
-        <v>95.689672</v>
+        <v>101.6702765</v>
       </c>
       <c r="N18">
-        <v>502.1336613333334</v>
+        <v>496.1530568333334</v>
       </c>
       <c r="O18">
-        <v>50.21336613333334</v>
+        <v>49.61530568333334</v>
       </c>
       <c r="P18">
-        <v>451.9202952000001</v>
+        <v>446.53775115</v>
       </c>
       <c r="Q18">
-        <v>457.9302952</v>
+        <v>452.54775115</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07809501776474989</v>
+        <v>0.07845089880094683</v>
       </c>
       <c r="T18">
-        <v>0.647310355035332</v>
+        <v>0.6544435135172082</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.247522024459792</v>
+        <v>5.880020728903332</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07329974600478587</v>
+        <v>0.0734252770871818</v>
       </c>
       <c r="C19">
-        <v>9984.947117315207</v>
+        <v>9821.5258113608</v>
       </c>
       <c r="D19">
-        <v>11849.22611731521</v>
+        <v>11797.5918113608</v>
       </c>
       <c r="E19">
-        <v>-1584.221</v>
+        <v>-1472.434</v>
       </c>
       <c r="F19">
-        <v>1900.379</v>
+        <v>2012.166</v>
       </c>
       <c r="G19">
         <v>36.1</v>
@@ -2845,45 +2845,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M19">
-        <v>101.6702765</v>
+        <v>109.2606138</v>
       </c>
       <c r="N19">
-        <v>496.1530568333334</v>
+        <v>488.5627195333333</v>
       </c>
       <c r="O19">
-        <v>49.61530568333334</v>
+        <v>48.85627195333333</v>
       </c>
       <c r="P19">
-        <v>446.53775115</v>
+        <v>439.70644758</v>
       </c>
       <c r="Q19">
-        <v>452.54775115</v>
+        <v>445.71644758</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07845089880094683</v>
+        <v>0.07881545986241684</v>
       </c>
       <c r="T19">
-        <v>0.6544435135172082</v>
+        <v>0.6617506514742522</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>5.880020728903332</v>
+        <v>5.471535556514814</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07342527708718181</v>
+        <v>0.07342840816957774</v>
       </c>
       <c r="C20">
-        <v>9821.525811360792</v>
+        <v>9708.456664586085</v>
       </c>
       <c r="D20">
-        <v>11797.59181136079</v>
+        <v>11796.30966458608</v>
       </c>
       <c r="E20">
-        <v>-1472.434</v>
+        <v>-1360.647</v>
       </c>
       <c r="F20">
-        <v>2012.166</v>
+        <v>2123.953</v>
       </c>
       <c r="G20">
         <v>36.1</v>
@@ -2927,28 +2927,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M20">
-        <v>109.2606138</v>
+        <v>115.3306479</v>
       </c>
       <c r="N20">
-        <v>488.5627195333334</v>
+        <v>482.4926854333333</v>
       </c>
       <c r="O20">
-        <v>48.85627195333334</v>
+        <v>48.24926854333334</v>
       </c>
       <c r="P20">
-        <v>439.70644758</v>
+        <v>434.24341689</v>
       </c>
       <c r="Q20">
-        <v>445.71644758</v>
+        <v>440.25341689</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07881545986241684</v>
+        <v>0.07918902243157747</v>
       </c>
       <c r="T20">
-        <v>0.6617506514742522</v>
+        <v>0.6692382125907294</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.471535556514816</v>
+        <v>5.183560000908773</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07342840816957774</v>
+        <v>0.0734315392519737</v>
       </c>
       <c r="C21">
-        <v>9708.456664586085</v>
+        <v>9595.387796465135</v>
       </c>
       <c r="D21">
-        <v>11796.30966458608</v>
+        <v>11795.02779646513</v>
       </c>
       <c r="E21">
-        <v>-1360.647</v>
+        <v>-1248.86</v>
       </c>
       <c r="F21">
-        <v>2123.953</v>
+        <v>2235.74</v>
       </c>
       <c r="G21">
         <v>36.1</v>
@@ -3009,28 +3009,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M21">
-        <v>115.3306479</v>
+        <v>121.400682</v>
       </c>
       <c r="N21">
-        <v>482.4926854333333</v>
+        <v>476.4226513333334</v>
       </c>
       <c r="O21">
-        <v>48.24926854333334</v>
+        <v>47.64226513333334</v>
       </c>
       <c r="P21">
-        <v>434.24341689</v>
+        <v>428.7803862</v>
       </c>
       <c r="Q21">
-        <v>440.25341689</v>
+        <v>434.7903862</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07918902243157747</v>
+        <v>0.07957192406496712</v>
       </c>
       <c r="T21">
-        <v>0.6692382125907294</v>
+        <v>0.6769129627351185</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.183560000908773</v>
+        <v>4.924382000863334</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0734315392519737</v>
+        <v>0.07343467033436965</v>
       </c>
       <c r="C22">
-        <v>9595.387796465135</v>
+        <v>9482.319206907121</v>
       </c>
       <c r="D22">
-        <v>11795.02779646513</v>
+        <v>11793.74620690712</v>
       </c>
       <c r="E22">
-        <v>-1248.86</v>
+        <v>-1137.072999999999</v>
       </c>
       <c r="F22">
-        <v>2235.74</v>
+        <v>2347.527</v>
       </c>
       <c r="G22">
         <v>36.1</v>
@@ -3091,28 +3091,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M22">
-        <v>121.400682</v>
+        <v>127.4707161</v>
       </c>
       <c r="N22">
-        <v>476.4226513333334</v>
+        <v>470.3526172333334</v>
       </c>
       <c r="O22">
-        <v>47.64226513333334</v>
+        <v>47.03526172333334</v>
       </c>
       <c r="P22">
-        <v>428.7803862</v>
+        <v>423.31735551</v>
       </c>
       <c r="Q22">
-        <v>434.7903862</v>
+        <v>429.32735551</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07957192406496712</v>
+        <v>0.07996451941059449</v>
       </c>
       <c r="T22">
-        <v>0.6769129627351185</v>
+        <v>0.6847820103515174</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.924382000863334</v>
+        <v>4.689887619869841</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07343467033436965</v>
+        <v>0.07343780141676559</v>
       </c>
       <c r="C23">
-        <v>9482.319206907121</v>
+        <v>9369.250895821262</v>
       </c>
       <c r="D23">
-        <v>11793.74620690712</v>
+        <v>11792.46489582126</v>
       </c>
       <c r="E23">
-        <v>-1137.073</v>
+        <v>-1025.286</v>
       </c>
       <c r="F23">
-        <v>2347.527</v>
+        <v>2459.314</v>
       </c>
       <c r="G23">
         <v>36.1</v>
@@ -3173,28 +3173,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M23">
-        <v>127.4707161</v>
+        <v>133.5407502</v>
       </c>
       <c r="N23">
-        <v>470.3526172333334</v>
+        <v>464.2825831333333</v>
       </c>
       <c r="O23">
-        <v>47.03526172333334</v>
+        <v>46.42825831333334</v>
       </c>
       <c r="P23">
-        <v>423.31735551</v>
+        <v>417.85432482</v>
       </c>
       <c r="Q23">
-        <v>429.32735551</v>
+        <v>423.86432482</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07996451941059449</v>
+        <v>0.08036718130354562</v>
       </c>
       <c r="T23">
-        <v>0.6847820103515174</v>
+        <v>0.6928528284196189</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.689887619869842</v>
+        <v>4.476710909875758</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07343780141676559</v>
+        <v>0.07344093249916153</v>
       </c>
       <c r="C24">
-        <v>9369.250895821262</v>
+        <v>9256.182863116794</v>
       </c>
       <c r="D24">
-        <v>11792.46489582126</v>
+        <v>11791.18386311679</v>
       </c>
       <c r="E24">
-        <v>-1025.286</v>
+        <v>-913.4989999999998</v>
       </c>
       <c r="F24">
-        <v>2459.314</v>
+        <v>2571.101</v>
       </c>
       <c r="G24">
         <v>36.1</v>
@@ -3255,28 +3255,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M24">
-        <v>133.5407502</v>
+        <v>139.6107843</v>
       </c>
       <c r="N24">
-        <v>464.2825831333333</v>
+        <v>458.2125490333334</v>
       </c>
       <c r="O24">
-        <v>46.42825831333334</v>
+        <v>45.82125490333334</v>
       </c>
       <c r="P24">
-        <v>417.85432482</v>
+        <v>412.3912941300001</v>
       </c>
       <c r="Q24">
-        <v>423.86432482</v>
+        <v>418.4012941300001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08036718130354562</v>
+        <v>0.08078030194696303</v>
       </c>
       <c r="T24">
-        <v>0.6928528284196189</v>
+        <v>0.7011332781258529</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.476710909875758</v>
+        <v>4.282071305098551</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07344093249916153</v>
+        <v>0.07366006358155748</v>
       </c>
       <c r="C25">
-        <v>9256.182863116794</v>
+        <v>9055.427987141633</v>
       </c>
       <c r="D25">
-        <v>11791.18386311679</v>
+        <v>11702.21598714163</v>
       </c>
       <c r="E25">
-        <v>-913.4989999999998</v>
+        <v>-801.7119999999995</v>
       </c>
       <c r="F25">
-        <v>2571.101</v>
+        <v>2682.888</v>
       </c>
       <c r="G25">
         <v>36.1</v>
@@ -3337,45 +3337,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M25">
-        <v>139.6107843</v>
+        <v>148.3637064</v>
       </c>
       <c r="N25">
-        <v>458.2125490333334</v>
+        <v>449.4596269333334</v>
       </c>
       <c r="O25">
-        <v>45.82125490333334</v>
+        <v>44.94596269333334</v>
       </c>
       <c r="P25">
-        <v>412.3912941300001</v>
+        <v>404.51366424</v>
       </c>
       <c r="Q25">
-        <v>418.4012941300001</v>
+        <v>410.52366424</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08078030194696303</v>
+        <v>0.08120429418625984</v>
       </c>
       <c r="T25">
-        <v>0.7011332781258529</v>
+        <v>0.7096316344033036</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.1</v>
       </c>
       <c r="W25">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.282071305098551</v>
+        <v>4.029444584793234</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07366006358155748</v>
+        <v>0.07367219466395342</v>
       </c>
       <c r="C26">
-        <v>9055.427987141633</v>
+        <v>8938.754934752949</v>
       </c>
       <c r="D26">
-        <v>11702.21598714163</v>
+        <v>11697.32993475295</v>
       </c>
       <c r="E26">
-        <v>-801.712</v>
+        <v>-689.9249999999997</v>
       </c>
       <c r="F26">
-        <v>2682.888</v>
+        <v>2794.675</v>
       </c>
       <c r="G26">
         <v>36.1</v>
@@ -3419,28 +3419,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M26">
-        <v>148.3637064</v>
+        <v>154.5455275</v>
       </c>
       <c r="N26">
-        <v>449.4596269333334</v>
+        <v>443.2778058333333</v>
       </c>
       <c r="O26">
-        <v>44.94596269333334</v>
+        <v>44.32778058333334</v>
       </c>
       <c r="P26">
-        <v>404.51366424</v>
+        <v>398.95002525</v>
       </c>
       <c r="Q26">
-        <v>410.52366424</v>
+        <v>404.96002525</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08120429418625984</v>
+        <v>0.08163959288527123</v>
       </c>
       <c r="T26">
-        <v>0.7096316344033036</v>
+        <v>0.7183566135148196</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.029444584793234</v>
+        <v>3.868266801401504</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07367219466395342</v>
+        <v>0.07368432574634937</v>
       </c>
       <c r="C27">
-        <v>8938.754934752949</v>
+        <v>8822.085960830114</v>
       </c>
       <c r="D27">
-        <v>11697.32993475295</v>
+        <v>11692.44796083011</v>
       </c>
       <c r="E27">
-        <v>-689.9249999999997</v>
+        <v>-578.1379999999995</v>
       </c>
       <c r="F27">
-        <v>2794.675</v>
+        <v>2906.462</v>
       </c>
       <c r="G27">
         <v>36.1</v>
@@ -3501,28 +3501,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M27">
-        <v>154.5455275</v>
+        <v>160.7273486</v>
       </c>
       <c r="N27">
-        <v>443.2778058333333</v>
+        <v>437.0959847333334</v>
       </c>
       <c r="O27">
-        <v>44.32778058333334</v>
+        <v>43.70959847333334</v>
       </c>
       <c r="P27">
-        <v>398.95002525</v>
+        <v>393.38638626</v>
       </c>
       <c r="Q27">
-        <v>404.96002525</v>
+        <v>399.39638626</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08163959288527123</v>
+        <v>0.08208665641398563</v>
       </c>
       <c r="T27">
-        <v>0.7183566135148196</v>
+        <v>0.7273174028725928</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.868266801401504</v>
+        <v>3.719487309039908</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07368432574634937</v>
+        <v>0.07369645682874532</v>
       </c>
       <c r="C28">
-        <v>8822.085960830114</v>
+        <v>8705.421060268722</v>
       </c>
       <c r="D28">
-        <v>11692.44796083011</v>
+        <v>11687.57006026872</v>
       </c>
       <c r="E28">
-        <v>-578.1379999999995</v>
+        <v>-466.3509999999997</v>
       </c>
       <c r="F28">
-        <v>2906.462</v>
+        <v>3018.249</v>
       </c>
       <c r="G28">
         <v>36.1</v>
@@ -3583,28 +3583,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M28">
-        <v>160.7273486</v>
+        <v>166.9091697</v>
       </c>
       <c r="N28">
-        <v>437.0959847333334</v>
+        <v>430.9141636333334</v>
       </c>
       <c r="O28">
-        <v>43.70959847333334</v>
+        <v>43.09141636333334</v>
       </c>
       <c r="P28">
-        <v>393.38638626</v>
+        <v>387.82274727</v>
       </c>
       <c r="Q28">
-        <v>399.39638626</v>
+        <v>393.83274727</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08208665641398563</v>
+        <v>0.08254596825855523</v>
       </c>
       <c r="T28">
-        <v>0.7273174028725928</v>
+        <v>0.7365236933086613</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.719487309039908</v>
+        <v>3.581728519816208</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07369645682874532</v>
+        <v>0.07370858791114127</v>
       </c>
       <c r="C29">
-        <v>8705.421060268722</v>
+        <v>8588.760227972871</v>
       </c>
       <c r="D29">
-        <v>11687.57006026872</v>
+        <v>11682.69622797287</v>
       </c>
       <c r="E29">
-        <v>-466.3509999999997</v>
+        <v>-354.5639999999994</v>
       </c>
       <c r="F29">
-        <v>3018.249</v>
+        <v>3130.036000000001</v>
       </c>
       <c r="G29">
         <v>36.1</v>
@@ -3665,28 +3665,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M29">
-        <v>166.9091697</v>
+        <v>173.0909908</v>
       </c>
       <c r="N29">
-        <v>430.9141636333334</v>
+        <v>424.7323425333333</v>
       </c>
       <c r="O29">
-        <v>43.09141636333334</v>
+        <v>42.47323425333334</v>
       </c>
       <c r="P29">
-        <v>387.82274727</v>
+        <v>382.25910828</v>
       </c>
       <c r="Q29">
-        <v>393.83274727</v>
+        <v>388.26910828</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08254596825855523</v>
+        <v>0.08301803876547398</v>
       </c>
       <c r="T29">
-        <v>0.7365236933086613</v>
+        <v>0.7459857140346204</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.581728519816208</v>
+        <v>3.453809644108486</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07370858791114127</v>
+        <v>0.07372071899353722</v>
       </c>
       <c r="C30">
-        <v>8588.760227972871</v>
+        <v>8472.103458855165</v>
       </c>
       <c r="D30">
-        <v>11682.69622797287</v>
+        <v>11677.82645885516</v>
       </c>
       <c r="E30">
-        <v>-354.5639999999994</v>
+        <v>-242.7769999999991</v>
       </c>
       <c r="F30">
-        <v>3130.036000000001</v>
+        <v>3241.823000000001</v>
       </c>
       <c r="G30">
         <v>36.1</v>
@@ -3747,28 +3747,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M30">
-        <v>173.0909908</v>
+        <v>179.2728119000001</v>
       </c>
       <c r="N30">
-        <v>424.7323425333333</v>
+        <v>418.5505214333333</v>
       </c>
       <c r="O30">
-        <v>42.47323425333334</v>
+        <v>41.85505214333333</v>
       </c>
       <c r="P30">
-        <v>382.25910828</v>
+        <v>376.6954692899999</v>
       </c>
       <c r="Q30">
-        <v>388.26910828</v>
+        <v>382.7054692899999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08301803876547398</v>
+        <v>0.083503407033151</v>
       </c>
       <c r="T30">
-        <v>0.7459857140346204</v>
+        <v>0.7557142705556771</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.453809644108486</v>
+        <v>3.334712759828883</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0737207189935372</v>
+        <v>0.07373285007593314</v>
       </c>
       <c r="C31">
-        <v>8472.103458855172</v>
+        <v>8355.450747836698</v>
       </c>
       <c r="D31">
-        <v>11677.82645885517</v>
+        <v>11672.9607478367</v>
       </c>
       <c r="E31">
-        <v>-242.777</v>
+        <v>-130.9899999999998</v>
       </c>
       <c r="F31">
-        <v>3241.823</v>
+        <v>3353.61</v>
       </c>
       <c r="G31">
         <v>36.1</v>
@@ -3829,28 +3829,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M31">
-        <v>179.2728119</v>
+        <v>185.454633</v>
       </c>
       <c r="N31">
-        <v>418.5505214333334</v>
+        <v>412.3687003333334</v>
       </c>
       <c r="O31">
-        <v>41.85505214333335</v>
+        <v>41.23687003333334</v>
       </c>
       <c r="P31">
-        <v>376.6954692900001</v>
+        <v>371.1318303</v>
       </c>
       <c r="Q31">
-        <v>382.7054692900001</v>
+        <v>377.1418303</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08350340703315098</v>
+        <v>0.08400264296561878</v>
       </c>
       <c r="T31">
-        <v>0.755714270555677</v>
+        <v>0.765720785834478</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.334712759828884</v>
+        <v>3.223555667834588</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07373285007593314</v>
+        <v>0.07374498115832909</v>
       </c>
       <c r="C32">
-        <v>8355.450747836698</v>
+        <v>8238.802089846986</v>
       </c>
       <c r="D32">
-        <v>11672.9607478367</v>
+        <v>11668.09908984699</v>
       </c>
       <c r="E32">
-        <v>-130.9899999999998</v>
+        <v>-19.20299999999952</v>
       </c>
       <c r="F32">
-        <v>3353.61</v>
+        <v>3465.397</v>
       </c>
       <c r="G32">
         <v>36.1</v>
@@ -3911,28 +3911,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M32">
-        <v>185.454633</v>
+        <v>191.6364541</v>
       </c>
       <c r="N32">
-        <v>412.3687003333334</v>
+        <v>406.1868792333333</v>
       </c>
       <c r="O32">
-        <v>41.23687003333334</v>
+        <v>40.61868792333334</v>
       </c>
       <c r="P32">
-        <v>371.1318303</v>
+        <v>365.56819131</v>
       </c>
       <c r="Q32">
-        <v>377.1418303</v>
+        <v>371.57819131</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08400264296561878</v>
+        <v>0.08451634950482477</v>
       </c>
       <c r="T32">
-        <v>0.765720785834478</v>
+        <v>0.7760173450344038</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.223555667834588</v>
+        <v>3.119570001130246</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07374498115832909</v>
+        <v>0.07375711224072504</v>
       </c>
       <c r="C33">
-        <v>8238.802089846986</v>
+        <v>8122.157479824024</v>
       </c>
       <c r="D33">
-        <v>11668.09908984699</v>
+        <v>11663.24147982402</v>
       </c>
       <c r="E33">
-        <v>-19.20299999999952</v>
+        <v>92.58400000000029</v>
       </c>
       <c r="F33">
-        <v>3465.397</v>
+        <v>3577.184</v>
       </c>
       <c r="G33">
         <v>36.1</v>
@@ -3993,28 +3993,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M33">
-        <v>191.6364541</v>
+        <v>197.8182752</v>
       </c>
       <c r="N33">
-        <v>406.1868792333333</v>
+        <v>400.0050581333334</v>
       </c>
       <c r="O33">
-        <v>40.61868792333334</v>
+        <v>40.00050581333334</v>
       </c>
       <c r="P33">
-        <v>365.56819131</v>
+        <v>360.00455232</v>
       </c>
       <c r="Q33">
-        <v>371.57819131</v>
+        <v>366.01455232</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08451634950482477</v>
+        <v>0.08504516505988977</v>
       </c>
       <c r="T33">
-        <v>0.7760173450344038</v>
+        <v>0.786616744210798</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.119570001130246</v>
+        <v>3.022083438594926</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07375711224072504</v>
+        <v>0.07451174332312098</v>
       </c>
       <c r="C34">
-        <v>8122.157479824024</v>
+        <v>7715.946638655864</v>
       </c>
       <c r="D34">
-        <v>11663.24147982402</v>
+        <v>11368.81763865586</v>
       </c>
       <c r="E34">
-        <v>92.58400000000029</v>
+        <v>204.3710000000005</v>
       </c>
       <c r="F34">
-        <v>3577.184</v>
+        <v>3688.971</v>
       </c>
       <c r="G34">
         <v>36.1</v>
@@ -4075,45 +4075,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M34">
-        <v>197.8182752</v>
+        <v>213.2225238</v>
       </c>
       <c r="N34">
-        <v>400.0050581333334</v>
+        <v>384.6008095333333</v>
       </c>
       <c r="O34">
-        <v>40.00050581333334</v>
+        <v>38.46008095333334</v>
       </c>
       <c r="P34">
-        <v>360.00455232</v>
+        <v>346.14072858</v>
       </c>
       <c r="Q34">
-        <v>366.01455232</v>
+        <v>352.15072858</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08504516505988977</v>
+        <v>0.08558976615391192</v>
       </c>
       <c r="T34">
-        <v>0.786616744210798</v>
+        <v>0.7975325433626068</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.1</v>
       </c>
       <c r="W34">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.022083438594926</v>
+        <v>2.803753199610769</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07451174332312098</v>
+        <v>0.07454637440551692</v>
       </c>
       <c r="C35">
-        <v>7715.946638655864</v>
+        <v>7591.004435563894</v>
       </c>
       <c r="D35">
-        <v>11368.81763865586</v>
+        <v>11355.66243556389</v>
       </c>
       <c r="E35">
-        <v>204.3710000000005</v>
+        <v>316.1580000000008</v>
       </c>
       <c r="F35">
-        <v>3688.971</v>
+        <v>3800.758000000001</v>
       </c>
       <c r="G35">
         <v>36.1</v>
@@ -4157,28 +4157,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M35">
-        <v>213.2225238</v>
+        <v>219.6838124000001</v>
       </c>
       <c r="N35">
-        <v>384.6008095333333</v>
+        <v>378.1395209333333</v>
       </c>
       <c r="O35">
-        <v>38.46008095333334</v>
+        <v>37.81395209333333</v>
       </c>
       <c r="P35">
-        <v>346.14072858</v>
+        <v>340.32556884</v>
       </c>
       <c r="Q35">
-        <v>352.15072858</v>
+        <v>346.33556884</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08558976615391192</v>
+        <v>0.08615087031138929</v>
       </c>
       <c r="T35">
-        <v>0.7975325433626068</v>
+        <v>0.8087791243068949</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.803753199610769</v>
+        <v>2.721289870210452</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07454637440551692</v>
+        <v>0.07458100548791287</v>
       </c>
       <c r="C36">
-        <v>7591.004435563894</v>
+        <v>7466.092641851883</v>
       </c>
       <c r="D36">
-        <v>11355.66243556389</v>
+        <v>11342.53764185188</v>
       </c>
       <c r="E36">
-        <v>316.1580000000008</v>
+        <v>427.9450000000006</v>
       </c>
       <c r="F36">
-        <v>3800.758000000001</v>
+        <v>3912.545000000001</v>
       </c>
       <c r="G36">
         <v>36.1</v>
@@ -4239,28 +4239,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M36">
-        <v>219.6838124000001</v>
+        <v>226.145101</v>
       </c>
       <c r="N36">
-        <v>378.1395209333333</v>
+        <v>371.6782323333333</v>
       </c>
       <c r="O36">
-        <v>37.81395209333333</v>
+        <v>37.16782323333333</v>
       </c>
       <c r="P36">
-        <v>340.32556884</v>
+        <v>334.5104091</v>
       </c>
       <c r="Q36">
-        <v>346.33556884</v>
+        <v>340.5204091</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08615087031138929</v>
+        <v>0.08672923921217365</v>
       </c>
       <c r="T36">
-        <v>0.8087791243068949</v>
+        <v>0.8203717538956224</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.721289870210452</v>
+        <v>2.643538731061582</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07458100548791287</v>
+        <v>0.07461563657030881</v>
       </c>
       <c r="C37">
-        <v>7466.092641851883</v>
+        <v>7341.211152200716</v>
       </c>
       <c r="D37">
-        <v>11342.53764185188</v>
+        <v>11329.44315220072</v>
       </c>
       <c r="E37">
-        <v>427.9450000000006</v>
+        <v>539.7320000000009</v>
       </c>
       <c r="F37">
-        <v>3912.545000000001</v>
+        <v>4024.332000000001</v>
       </c>
       <c r="G37">
         <v>36.1</v>
@@ -4321,28 +4321,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M37">
-        <v>226.145101</v>
+        <v>232.6063896000001</v>
       </c>
       <c r="N37">
-        <v>371.6782323333333</v>
+        <v>365.2169437333333</v>
       </c>
       <c r="O37">
-        <v>37.16782323333333</v>
+        <v>36.52169437333333</v>
       </c>
       <c r="P37">
-        <v>334.5104091</v>
+        <v>328.69524936</v>
       </c>
       <c r="Q37">
-        <v>340.5204091</v>
+        <v>334.70524936</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08672923921217365</v>
+        <v>0.08732568214110753</v>
       </c>
       <c r="T37">
-        <v>0.8203717538956224</v>
+        <v>0.8323266531589978</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.643538731061582</v>
+        <v>2.570107099643204</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07461563657030881</v>
+        <v>0.07465026765270477</v>
       </c>
       <c r="C38">
-        <v>7341.211152200716</v>
+        <v>7216.359861777073</v>
       </c>
       <c r="D38">
-        <v>11329.44315220072</v>
+        <v>11316.37886177707</v>
       </c>
       <c r="E38">
-        <v>539.7320000000004</v>
+        <v>651.5190000000007</v>
       </c>
       <c r="F38">
-        <v>4024.332</v>
+        <v>4136.119000000001</v>
       </c>
       <c r="G38">
         <v>36.1</v>
@@ -4403,28 +4403,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M38">
-        <v>232.6063896</v>
+        <v>239.0676782</v>
       </c>
       <c r="N38">
-        <v>365.2169437333333</v>
+        <v>358.7556551333333</v>
       </c>
       <c r="O38">
-        <v>36.52169437333333</v>
+        <v>35.87556551333333</v>
       </c>
       <c r="P38">
-        <v>328.69524936</v>
+        <v>322.88008962</v>
       </c>
       <c r="Q38">
-        <v>334.70524936</v>
+        <v>328.89008962</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08732568214110753</v>
+        <v>0.08794105976619804</v>
       </c>
       <c r="T38">
-        <v>0.8323266531589978</v>
+        <v>0.8446610730339087</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.570107099643205</v>
+        <v>2.500644745598794</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07465026765270477</v>
+        <v>0.07588189873510072</v>
       </c>
       <c r="C39">
-        <v>7216.359861777073</v>
+        <v>6658.768480185473</v>
       </c>
       <c r="D39">
-        <v>11316.37886177707</v>
+        <v>10870.57448018547</v>
       </c>
       <c r="E39">
-        <v>651.5190000000007</v>
+        <v>763.306</v>
       </c>
       <c r="F39">
-        <v>4136.119000000001</v>
+        <v>4247.906</v>
       </c>
       <c r="G39">
         <v>36.1</v>
@@ -4485,45 +4485,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M39">
-        <v>239.0676782</v>
+        <v>260.3966378</v>
       </c>
       <c r="N39">
-        <v>358.7556551333333</v>
+        <v>337.4266955333334</v>
       </c>
       <c r="O39">
-        <v>35.87556551333333</v>
+        <v>33.74266955333334</v>
       </c>
       <c r="P39">
-        <v>322.88008962</v>
+        <v>303.6840259800001</v>
       </c>
       <c r="Q39">
-        <v>328.89008962</v>
+        <v>309.69402598</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08794105976619804</v>
+        <v>0.08857628828242051</v>
       </c>
       <c r="T39">
-        <v>0.8446610730339087</v>
+        <v>0.8573933774209138</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.1</v>
       </c>
       <c r="W39">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.500644745598794</v>
+        <v>2.295818173322564</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07588189873510072</v>
+        <v>0.07693082981749666</v>
       </c>
       <c r="C40">
-        <v>6658.768480185473</v>
+        <v>6194.104094543393</v>
       </c>
       <c r="D40">
-        <v>10870.57448018547</v>
+        <v>10517.69709454339</v>
       </c>
       <c r="E40">
-        <v>763.306</v>
+        <v>875.0930000000003</v>
       </c>
       <c r="F40">
-        <v>4247.906</v>
+        <v>4359.693</v>
       </c>
       <c r="G40">
         <v>36.1</v>
@@ -4567,45 +4567,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M40">
-        <v>260.3966378</v>
+        <v>279.4563213</v>
       </c>
       <c r="N40">
-        <v>337.4266955333334</v>
+        <v>318.3670120333334</v>
       </c>
       <c r="O40">
-        <v>33.74266955333334</v>
+        <v>31.83670120333334</v>
       </c>
       <c r="P40">
-        <v>303.6840259800001</v>
+        <v>286.53031083</v>
       </c>
       <c r="Q40">
-        <v>309.69402598</v>
+        <v>292.54031083</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08857628828242051</v>
+        <v>0.08923234396310926</v>
       </c>
       <c r="T40">
-        <v>0.8573933774209138</v>
+        <v>0.8705431344107712</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.1</v>
       </c>
       <c r="W40">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.295818173322564</v>
+        <v>2.139237110659459</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07693082981749666</v>
+        <v>0.07702216089989261</v>
       </c>
       <c r="C41">
-        <v>6194.104094543393</v>
+        <v>6052.673022818782</v>
       </c>
       <c r="D41">
-        <v>10517.69709454339</v>
+        <v>10488.05302281878</v>
       </c>
       <c r="E41">
-        <v>875.0930000000003</v>
+        <v>986.8800000000006</v>
       </c>
       <c r="F41">
-        <v>4359.693</v>
+        <v>4471.48</v>
       </c>
       <c r="G41">
         <v>36.1</v>
@@ -4649,28 +4649,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M41">
-        <v>279.4563213</v>
+        <v>286.6218680000001</v>
       </c>
       <c r="N41">
-        <v>318.3670120333334</v>
+        <v>311.2014653333333</v>
       </c>
       <c r="O41">
-        <v>31.83670120333334</v>
+        <v>31.12014653333333</v>
       </c>
       <c r="P41">
-        <v>286.53031083</v>
+        <v>280.0813188</v>
       </c>
       <c r="Q41">
-        <v>292.54031083</v>
+        <v>286.0913188</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08923234396310926</v>
+        <v>0.08991026816648767</v>
       </c>
       <c r="T41">
-        <v>0.8705431344107712</v>
+        <v>0.8841312166336242</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.139237110659459</v>
+        <v>2.085756182892972</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07702216089989261</v>
+        <v>0.07711349198228855</v>
       </c>
       <c r="C42">
-        <v>6052.673022818782</v>
+        <v>5911.408584746118</v>
       </c>
       <c r="D42">
-        <v>10488.05302281878</v>
+        <v>10458.57558474612</v>
       </c>
       <c r="E42">
-        <v>986.8800000000006</v>
+        <v>1098.667000000001</v>
       </c>
       <c r="F42">
-        <v>4471.48</v>
+        <v>4583.267000000001</v>
       </c>
       <c r="G42">
         <v>36.1</v>
@@ -4731,28 +4731,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M42">
-        <v>286.6218680000001</v>
+        <v>293.7874147000001</v>
       </c>
       <c r="N42">
-        <v>311.2014653333333</v>
+        <v>304.0359186333333</v>
       </c>
       <c r="O42">
-        <v>31.12014653333333</v>
+        <v>30.40359186333333</v>
       </c>
       <c r="P42">
-        <v>280.0813188</v>
+        <v>273.63232677</v>
       </c>
       <c r="Q42">
-        <v>286.0913188</v>
+        <v>279.64232677</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08991026816648767</v>
+        <v>0.09061117285133652</v>
       </c>
       <c r="T42">
-        <v>0.8841312166336242</v>
+        <v>0.8981799118131838</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.085756182892972</v>
+        <v>2.034884080871192</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07711349198228855</v>
+        <v>0.08015322306468449</v>
       </c>
       <c r="C43">
-        <v>5911.408584746118</v>
+        <v>4904.982052770359</v>
       </c>
       <c r="D43">
-        <v>10458.57558474612</v>
+        <v>9563.936052770359</v>
       </c>
       <c r="E43">
-        <v>1098.667000000001</v>
+        <v>1210.454000000001</v>
       </c>
       <c r="F43">
-        <v>4583.267000000001</v>
+        <v>4695.054000000001</v>
       </c>
       <c r="G43">
         <v>36.1</v>
@@ -4813,45 +4813,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M43">
-        <v>293.7874147000001</v>
+        <v>337.5743826000001</v>
       </c>
       <c r="N43">
-        <v>304.0359186333333</v>
+        <v>260.2489507333333</v>
       </c>
       <c r="O43">
-        <v>30.40359186333333</v>
+        <v>26.02489507333333</v>
       </c>
       <c r="P43">
-        <v>273.63232677</v>
+        <v>234.2240556599999</v>
       </c>
       <c r="Q43">
-        <v>279.64232677</v>
+        <v>240.2340556599999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09061117285133652</v>
+        <v>0.09133624666324913</v>
       </c>
       <c r="T43">
-        <v>0.8981799118131838</v>
+        <v>0.912713044757556</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.1</v>
       </c>
       <c r="W43">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.034884080871192</v>
+        <v>1.770938092899391</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0801532230646845</v>
+        <v>0.08182405414708044</v>
       </c>
       <c r="C44">
-        <v>4904.982052770354</v>
+        <v>4363.703082883521</v>
       </c>
       <c r="D44">
-        <v>9563.936052770354</v>
+        <v>9134.444082883521</v>
       </c>
       <c r="E44">
-        <v>1210.454</v>
+        <v>1322.241</v>
       </c>
       <c r="F44">
-        <v>4695.054</v>
+        <v>4806.841</v>
       </c>
       <c r="G44">
         <v>36.1</v>
@@ -4895,45 +4895,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M44">
-        <v>337.5743826</v>
+        <v>364.3585478000001</v>
       </c>
       <c r="N44">
-        <v>260.2489507333333</v>
+        <v>233.4647855333333</v>
       </c>
       <c r="O44">
-        <v>26.02489507333334</v>
+        <v>23.34647855333333</v>
       </c>
       <c r="P44">
-        <v>234.22405566</v>
+        <v>210.11830698</v>
       </c>
       <c r="Q44">
-        <v>240.23405566</v>
+        <v>216.12830698</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09133624666324912</v>
+        <v>0.09208676166154461</v>
       </c>
       <c r="T44">
-        <v>0.9127130447575559</v>
+        <v>0.9277561121912041</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.1</v>
       </c>
       <c r="W44">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.770938092899391</v>
+        <v>1.640755615431546</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08182405414708044</v>
+        <v>0.08202068522947639</v>
       </c>
       <c r="C45">
-        <v>4363.703082883521</v>
+        <v>4203.895108873472</v>
       </c>
       <c r="D45">
-        <v>9134.444082883521</v>
+        <v>9086.423108873472</v>
       </c>
       <c r="E45">
-        <v>1322.241</v>
+        <v>1434.028000000001</v>
       </c>
       <c r="F45">
-        <v>4806.841</v>
+        <v>4918.628000000001</v>
       </c>
       <c r="G45">
         <v>36.1</v>
@@ -4977,28 +4977,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M45">
-        <v>364.3585478000001</v>
+        <v>372.8320024000001</v>
       </c>
       <c r="N45">
-        <v>233.4647855333333</v>
+        <v>224.9913309333333</v>
       </c>
       <c r="O45">
-        <v>23.34647855333333</v>
+        <v>22.49913309333333</v>
       </c>
       <c r="P45">
-        <v>210.11830698</v>
+        <v>202.49219784</v>
       </c>
       <c r="Q45">
-        <v>216.12830698</v>
+        <v>208.50219784</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09208676166154461</v>
+        <v>0.09286408076692211</v>
       </c>
       <c r="T45">
-        <v>0.9277561121912041</v>
+        <v>0.9433364320331973</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.640755615431546</v>
+        <v>1.603465715080829</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08202068522947639</v>
+        <v>0.08221731631187233</v>
       </c>
       <c r="C46">
-        <v>4203.895108873472</v>
+        <v>4044.589399545206</v>
       </c>
       <c r="D46">
-        <v>9086.423108873472</v>
+        <v>9038.904399545207</v>
       </c>
       <c r="E46">
-        <v>1434.028000000001</v>
+        <v>1545.815000000001</v>
       </c>
       <c r="F46">
-        <v>4918.628000000001</v>
+        <v>5030.415000000001</v>
       </c>
       <c r="G46">
         <v>36.1</v>
@@ -5059,28 +5059,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M46">
-        <v>372.8320024000001</v>
+        <v>381.3054570000001</v>
       </c>
       <c r="N46">
-        <v>224.9913309333333</v>
+        <v>216.5178763333333</v>
       </c>
       <c r="O46">
-        <v>22.49913309333333</v>
+        <v>21.65178763333333</v>
       </c>
       <c r="P46">
-        <v>202.49219784</v>
+        <v>194.8660886999999</v>
       </c>
       <c r="Q46">
-        <v>208.50219784</v>
+        <v>200.8760886999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09286408076692211</v>
+        <v>0.09366966602158605</v>
       </c>
       <c r="T46">
-        <v>0.9433364320331973</v>
+        <v>0.9594833089603534</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.603465715080829</v>
+        <v>1.567833143634588</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08221731631187233</v>
+        <v>0.08241394739426827</v>
       </c>
       <c r="C47">
-        <v>4044.589399545206</v>
+        <v>3885.778115905469</v>
       </c>
       <c r="D47">
-        <v>9038.904399545207</v>
+        <v>8991.880115905469</v>
       </c>
       <c r="E47">
-        <v>1545.815000000001</v>
+        <v>1657.602</v>
       </c>
       <c r="F47">
-        <v>5030.415000000001</v>
+        <v>5142.202</v>
       </c>
       <c r="G47">
         <v>36.1</v>
@@ -5141,28 +5141,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M47">
-        <v>381.3054570000001</v>
+        <v>389.7789116000001</v>
       </c>
       <c r="N47">
-        <v>216.5178763333333</v>
+        <v>208.0444217333333</v>
       </c>
       <c r="O47">
-        <v>21.65178763333333</v>
+        <v>20.80444217333333</v>
       </c>
       <c r="P47">
-        <v>194.8660886999999</v>
+        <v>187.23997956</v>
       </c>
       <c r="Q47">
-        <v>200.8760886999999</v>
+        <v>193.24997956</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09366966602158605</v>
+        <v>0.09450508776716346</v>
       </c>
       <c r="T47">
-        <v>0.9594833089603534</v>
+        <v>0.9762282183662933</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.567833143634588</v>
+        <v>1.53374981442514</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08241394739426827</v>
+        <v>0.08261057847666423</v>
       </c>
       <c r="C48">
-        <v>3885.778115905469</v>
+        <v>3727.453581244051</v>
       </c>
       <c r="D48">
-        <v>8991.880115905469</v>
+        <v>8945.342581244051</v>
       </c>
       <c r="E48">
-        <v>1657.602</v>
+        <v>1769.389000000001</v>
       </c>
       <c r="F48">
-        <v>5142.202</v>
+        <v>5253.989</v>
       </c>
       <c r="G48">
         <v>36.1</v>
@@ -5223,28 +5223,28 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M48">
-        <v>389.7789116000001</v>
+        <v>398.2523662000001</v>
       </c>
       <c r="N48">
-        <v>208.0444217333333</v>
+        <v>199.5709671333333</v>
       </c>
       <c r="O48">
-        <v>20.80444217333333</v>
+        <v>19.95709671333333</v>
       </c>
       <c r="P48">
-        <v>187.23997956</v>
+        <v>179.61387042</v>
       </c>
       <c r="Q48">
-        <v>193.24997956</v>
+        <v>185.6238704199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09450508776716346</v>
+        <v>0.09537203486163059</v>
       </c>
       <c r="T48">
-        <v>0.9762282183662933</v>
+        <v>0.9936050111460423</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.53374981442514</v>
+        <v>1.501116839650138</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08261057847666423</v>
+        <v>0.1017219086376846</v>
       </c>
       <c r="C49">
-        <v>3727.453581244051</v>
+        <v>621.8740516671833</v>
       </c>
       <c r="D49">
-        <v>8945.342581244051</v>
+        <v>5951.550051667184</v>
       </c>
       <c r="E49">
-        <v>1769.389000000001</v>
+        <v>1881.176000000001</v>
       </c>
       <c r="F49">
-        <v>5253.989</v>
+        <v>5365.776000000001</v>
       </c>
       <c r="G49">
         <v>36.1</v>
@@ -5305,45 +5305,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M49">
-        <v>398.2523662000001</v>
+        <v>636.3810336000001</v>
       </c>
       <c r="N49">
-        <v>199.5709671333333</v>
+        <v>-38.55770026666676</v>
       </c>
       <c r="O49">
-        <v>19.95709671333333</v>
+        <v>-3.855770026666676</v>
       </c>
       <c r="P49">
-        <v>179.61387042</v>
+        <v>-34.70193024000008</v>
       </c>
       <c r="Q49">
-        <v>185.6238704199999</v>
+        <v>-28.69193024000008</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09537203486163059</v>
+        <v>0.09642651440504273</v>
       </c>
       <c r="T49">
-        <v>0.9936050111460423</v>
+        <v>1.014740640567142</v>
       </c>
       <c r="U49">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V49">
-        <v>0.1</v>
+        <v>0.09394109845660448</v>
       </c>
       <c r="W49">
-        <v>0.06822</v>
+        <v>0.1074585857230467</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.501116839650138</v>
+        <v>0.9394109845660448</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1017219086376846</v>
+        <v>0.1024499086376846</v>
       </c>
       <c r="C50">
-        <v>621.8740516671842</v>
+        <v>435.1677722144668</v>
       </c>
       <c r="D50">
-        <v>5951.550051667184</v>
+        <v>5876.630772214467</v>
       </c>
       <c r="E50">
-        <v>1881.176</v>
+        <v>1992.963</v>
       </c>
       <c r="F50">
-        <v>5365.776</v>
+        <v>5477.563</v>
       </c>
       <c r="G50">
         <v>36.1</v>
@@ -5387,37 +5387,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M50">
-        <v>636.3810336</v>
+        <v>649.6389718</v>
       </c>
       <c r="N50">
-        <v>-38.55770026666664</v>
+        <v>-51.81563846666666</v>
       </c>
       <c r="O50">
-        <v>-3.855770026666665</v>
+        <v>-5.181563846666666</v>
       </c>
       <c r="P50">
-        <v>-34.70193023999998</v>
+        <v>-46.63407461999999</v>
       </c>
       <c r="Q50">
-        <v>-28.69193023999998</v>
+        <v>-40.62407461999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09642651440504273</v>
+        <v>0.09741919115808279</v>
       </c>
       <c r="T50">
-        <v>1.014740640567142</v>
+        <v>1.03463751587238</v>
       </c>
       <c r="U50">
         <v>0.1186</v>
       </c>
       <c r="V50">
-        <v>0.0939410984566045</v>
+        <v>0.09202393318197992</v>
       </c>
       <c r="W50">
-        <v>0.1074585857230467</v>
+        <v>0.1076859615246172</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.939410984566045</v>
+        <v>0.9202393318197991</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1024499086376846</v>
+        <v>0.1031779086376846</v>
       </c>
       <c r="C51">
-        <v>435.1677722144668</v>
+        <v>250.3242412883992</v>
       </c>
       <c r="D51">
-        <v>5876.630772214467</v>
+        <v>5803.574241288399</v>
       </c>
       <c r="E51">
-        <v>1992.963</v>
+        <v>2104.75</v>
       </c>
       <c r="F51">
-        <v>5477.563</v>
+        <v>5589.35</v>
       </c>
       <c r="G51">
         <v>36.1</v>
@@ -5469,37 +5469,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M51">
-        <v>649.6389718</v>
+        <v>662.89691</v>
       </c>
       <c r="N51">
-        <v>-51.81563846666666</v>
+        <v>-65.07357666666667</v>
       </c>
       <c r="O51">
-        <v>-5.181563846666666</v>
+        <v>-6.507357666666667</v>
       </c>
       <c r="P51">
-        <v>-46.63407461999999</v>
+        <v>-58.566219</v>
       </c>
       <c r="Q51">
-        <v>-40.62407461999999</v>
+        <v>-52.55621900000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09741919115808279</v>
+        <v>0.09845157498124443</v>
       </c>
       <c r="T51">
-        <v>1.03463751587238</v>
+        <v>1.055330266189828</v>
       </c>
       <c r="U51">
         <v>0.1186</v>
       </c>
       <c r="V51">
-        <v>0.09202393318197992</v>
+        <v>0.09018345451834031</v>
       </c>
       <c r="W51">
-        <v>0.1076859615246172</v>
+        <v>0.1079042422941248</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9202393318197991</v>
+        <v>0.9018345451834031</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1031779086376846</v>
+        <v>0.1039059086376846</v>
       </c>
       <c r="C52">
-        <v>250.3242412883992</v>
+        <v>67.27484052044201</v>
       </c>
       <c r="D52">
-        <v>5803.574241288399</v>
+        <v>5732.311840520442</v>
       </c>
       <c r="E52">
-        <v>2104.75</v>
+        <v>2216.537000000001</v>
       </c>
       <c r="F52">
-        <v>5589.35</v>
+        <v>5701.137000000001</v>
       </c>
       <c r="G52">
         <v>36.1</v>
@@ -5551,37 +5551,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M52">
-        <v>662.89691</v>
+        <v>676.1548482000002</v>
       </c>
       <c r="N52">
-        <v>-65.07357666666667</v>
+        <v>-78.33151486666679</v>
       </c>
       <c r="O52">
-        <v>-6.507357666666667</v>
+        <v>-7.833151486666679</v>
       </c>
       <c r="P52">
-        <v>-58.566219</v>
+        <v>-70.49836338000011</v>
       </c>
       <c r="Q52">
-        <v>-52.55621900000001</v>
+        <v>-64.48836338000011</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09845157498124443</v>
+        <v>0.09952609691963718</v>
       </c>
       <c r="T52">
-        <v>1.055330266189828</v>
+        <v>1.076867618561049</v>
       </c>
       <c r="U52">
         <v>0.1186</v>
       </c>
       <c r="V52">
-        <v>0.09018345451834031</v>
+        <v>0.08841515148856893</v>
       </c>
       <c r="W52">
-        <v>0.1079042422941248</v>
+        <v>0.1081139630334557</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9018345451834031</v>
+        <v>0.8841515148856892</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1039059086376846</v>
+        <v>0.1046339086376846</v>
       </c>
       <c r="C53">
-        <v>67.27484052044201</v>
+        <v>-114.0457190651532</v>
       </c>
       <c r="D53">
-        <v>5732.311840520442</v>
+        <v>5662.778280934847</v>
       </c>
       <c r="E53">
-        <v>2216.537000000001</v>
+        <v>2328.324000000001</v>
       </c>
       <c r="F53">
-        <v>5701.137000000001</v>
+        <v>5812.924000000001</v>
       </c>
       <c r="G53">
         <v>36.1</v>
@@ -5633,37 +5633,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M53">
-        <v>676.1548482000002</v>
+        <v>689.4127864000002</v>
       </c>
       <c r="N53">
-        <v>-78.33151486666679</v>
+        <v>-91.58945306666681</v>
       </c>
       <c r="O53">
-        <v>-7.833151486666679</v>
+        <v>-9.158945306666681</v>
       </c>
       <c r="P53">
-        <v>-70.49836338000011</v>
+        <v>-82.43050776000013</v>
       </c>
       <c r="Q53">
-        <v>-64.48836338000011</v>
+        <v>-76.42050776000012</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09952609691963718</v>
+        <v>0.1006453906054629</v>
       </c>
       <c r="T53">
-        <v>1.076867618561049</v>
+        <v>1.099302360614404</v>
       </c>
       <c r="U53">
         <v>0.1186</v>
       </c>
       <c r="V53">
-        <v>0.08841515148856893</v>
+        <v>0.08671486011378876</v>
       </c>
       <c r="W53">
-        <v>0.1081139630334557</v>
+        <v>0.1083156175905047</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8841515148856892</v>
+        <v>0.8671486011378875</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1046339086376846</v>
+        <v>0.1053619086376846</v>
       </c>
       <c r="C54">
-        <v>-114.0457190651532</v>
+        <v>-293.6995965607521</v>
       </c>
       <c r="D54">
-        <v>5662.778280934847</v>
+        <v>5594.911403439248</v>
       </c>
       <c r="E54">
-        <v>2328.324000000001</v>
+        <v>2440.111</v>
       </c>
       <c r="F54">
-        <v>5812.924000000001</v>
+        <v>5924.711</v>
       </c>
       <c r="G54">
         <v>36.1</v>
@@ -5715,37 +5715,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M54">
-        <v>689.4127864000002</v>
+        <v>702.6707246000001</v>
       </c>
       <c r="N54">
-        <v>-91.58945306666681</v>
+        <v>-104.8473912666667</v>
       </c>
       <c r="O54">
-        <v>-9.158945306666681</v>
+        <v>-10.48473912666667</v>
       </c>
       <c r="P54">
-        <v>-82.43050776000013</v>
+        <v>-94.36265214000004</v>
       </c>
       <c r="Q54">
-        <v>-76.42050776000012</v>
+        <v>-88.35265214000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1006453906054629</v>
+        <v>0.1018123138098345</v>
       </c>
       <c r="T54">
-        <v>1.099302360614404</v>
+        <v>1.12269177254237</v>
       </c>
       <c r="U54">
         <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.08671486011378876</v>
+        <v>0.08507873067767954</v>
       </c>
       <c r="W54">
-        <v>0.1083156175905047</v>
+        <v>0.1085096625416272</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8671486011378875</v>
+        <v>0.8507873067767954</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1053619086376846</v>
+        <v>0.1060899086376846</v>
       </c>
       <c r="C55">
-        <v>-293.6995965607521</v>
+        <v>-471.7460065082241</v>
       </c>
       <c r="D55">
-        <v>5594.911403439248</v>
+        <v>5528.651993491776</v>
       </c>
       <c r="E55">
-        <v>2440.111</v>
+        <v>2551.898000000001</v>
       </c>
       <c r="F55">
-        <v>5924.711</v>
+        <v>6036.498000000001</v>
       </c>
       <c r="G55">
         <v>36.1</v>
@@ -5797,37 +5797,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M55">
-        <v>702.6707246000001</v>
+        <v>715.9286628000001</v>
       </c>
       <c r="N55">
-        <v>-104.8473912666667</v>
+        <v>-118.1053294666667</v>
       </c>
       <c r="O55">
-        <v>-10.48473912666667</v>
+        <v>-11.81053294666667</v>
       </c>
       <c r="P55">
-        <v>-94.36265214000004</v>
+        <v>-106.29479652</v>
       </c>
       <c r="Q55">
-        <v>-88.35265214000003</v>
+        <v>-100.28479652</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1018123138098345</v>
+        <v>0.1030299728057005</v>
       </c>
       <c r="T55">
-        <v>1.12269177254237</v>
+        <v>1.147098115423726</v>
       </c>
       <c r="U55">
         <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.08507873067767954</v>
+        <v>0.08350319862809288</v>
       </c>
       <c r="W55">
-        <v>0.1085096625416272</v>
+        <v>0.1086965206427082</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8507873067767954</v>
+        <v>0.8350319862809288</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1060899086376846</v>
+        <v>0.1068179086376846</v>
       </c>
       <c r="C56">
-        <v>-471.7460065082241</v>
+        <v>-648.2413912168167</v>
       </c>
       <c r="D56">
-        <v>5528.651993491776</v>
+        <v>5463.943608783184</v>
       </c>
       <c r="E56">
-        <v>2551.898000000001</v>
+        <v>2663.685000000001</v>
       </c>
       <c r="F56">
-        <v>6036.498000000001</v>
+        <v>6148.285000000001</v>
       </c>
       <c r="G56">
         <v>36.1</v>
@@ -5879,37 +5879,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M56">
-        <v>715.9286628000001</v>
+        <v>729.1866010000001</v>
       </c>
       <c r="N56">
-        <v>-118.1053294666667</v>
+        <v>-131.3632676666667</v>
       </c>
       <c r="O56">
-        <v>-11.81053294666667</v>
+        <v>-13.13632676666667</v>
       </c>
       <c r="P56">
-        <v>-106.29479652</v>
+        <v>-118.2269409000001</v>
       </c>
       <c r="Q56">
-        <v>-100.28479652</v>
+        <v>-112.2169409000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1030299728057005</v>
+        <v>0.1043017499791605</v>
       </c>
       <c r="T56">
-        <v>1.147098115423726</v>
+        <v>1.172589184655365</v>
       </c>
       <c r="U56">
         <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.08350319862809288</v>
+        <v>0.08198495865303665</v>
       </c>
       <c r="W56">
-        <v>0.1086965206427082</v>
+        <v>0.1088765839037499</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8350319862809288</v>
+        <v>0.8198495865303664</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1068179086376846</v>
+        <v>0.1075459086376847</v>
       </c>
       <c r="C57">
-        <v>-648.2413912168167</v>
+        <v>-823.2395811199713</v>
       </c>
       <c r="D57">
-        <v>5463.943608783184</v>
+        <v>5400.732418880029</v>
       </c>
       <c r="E57">
-        <v>2663.685000000001</v>
+        <v>2775.472000000001</v>
       </c>
       <c r="F57">
-        <v>6148.285000000001</v>
+        <v>6260.072000000001</v>
       </c>
       <c r="G57">
         <v>36.1</v>
@@ -5961,37 +5961,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M57">
-        <v>729.1866010000001</v>
+        <v>742.4445392000002</v>
       </c>
       <c r="N57">
-        <v>-131.3632676666667</v>
+        <v>-144.6212058666669</v>
       </c>
       <c r="O57">
-        <v>-13.13632676666667</v>
+        <v>-14.46212058666669</v>
       </c>
       <c r="P57">
-        <v>-118.2269409000001</v>
+        <v>-130.1590852800002</v>
       </c>
       <c r="Q57">
-        <v>-112.2169409000001</v>
+        <v>-124.1490852800002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1043017499791605</v>
+        <v>0.1056313352059596</v>
       </c>
       <c r="T57">
-        <v>1.172589184655365</v>
+        <v>1.199238938852077</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.08198495865303665</v>
+        <v>0.08052094153423241</v>
       </c>
       <c r="W57">
-        <v>0.1088765839037499</v>
+        <v>0.1090502163340401</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8198495865303664</v>
+        <v>0.805209415342324</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1075459086376847</v>
+        <v>0.1556367995506536</v>
       </c>
       <c r="C58">
-        <v>-823.2395811199713</v>
+        <v>-3274.503543178141</v>
       </c>
       <c r="D58">
-        <v>5400.732418880029</v>
+        <v>3061.255456821861</v>
       </c>
       <c r="E58">
-        <v>2775.472000000001</v>
+        <v>2887.259000000001</v>
       </c>
       <c r="F58">
-        <v>6260.072000000001</v>
+        <v>6371.859000000001</v>
       </c>
       <c r="G58">
         <v>36.1</v>
@@ -6043,45 +6043,45 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M58">
-        <v>742.4445392000002</v>
+        <v>1279.4692872</v>
       </c>
       <c r="N58">
-        <v>-144.6212058666669</v>
+        <v>-681.6459538666669</v>
       </c>
       <c r="O58">
-        <v>-14.46212058666669</v>
+        <v>-68.16459538666669</v>
       </c>
       <c r="P58">
-        <v>-130.1590852800002</v>
+        <v>-613.4813584800002</v>
       </c>
       <c r="Q58">
-        <v>-124.1490852800002</v>
+        <v>-607.4713584800002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1056313352059596</v>
+        <v>0.1082062288455608</v>
       </c>
       <c r="T58">
-        <v>1.199238938852077</v>
+        <v>1.250849231441782</v>
       </c>
       <c r="U58">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08052094153423241</v>
+        <v>0.04672432072532309</v>
       </c>
       <c r="W58">
-        <v>0.1090502163340401</v>
+        <v>0.1914177563983551</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.805209415342324</v>
+        <v>0.467243207253231</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1556367995506536</v>
+        <v>0.1571867995506536</v>
       </c>
       <c r="C59">
-        <v>-3274.503543178141</v>
+        <v>-3428.442045196932</v>
       </c>
       <c r="D59">
-        <v>3061.255456821861</v>
+        <v>3019.103954803069</v>
       </c>
       <c r="E59">
-        <v>2887.259000000001</v>
+        <v>2999.046000000002</v>
       </c>
       <c r="F59">
-        <v>6371.859000000001</v>
+        <v>6483.646000000002</v>
       </c>
       <c r="G59">
         <v>36.1</v>
@@ -6125,37 +6125,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M59">
-        <v>1279.4692872</v>
+        <v>1301.9161168</v>
       </c>
       <c r="N59">
-        <v>-681.6459538666669</v>
+        <v>-704.0927834666669</v>
       </c>
       <c r="O59">
-        <v>-68.16459538666669</v>
+        <v>-70.4092783466667</v>
       </c>
       <c r="P59">
-        <v>-613.4813584800002</v>
+        <v>-633.6835051200002</v>
       </c>
       <c r="Q59">
-        <v>-607.4713584800002</v>
+        <v>-627.6735051200002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1082062288455608</v>
+        <v>0.1096920914371217</v>
       </c>
       <c r="T59">
-        <v>1.250849231441782</v>
+        <v>1.28063135599992</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.04672432072532309</v>
+        <v>0.0459187289886796</v>
       </c>
       <c r="W59">
-        <v>0.1914177563983551</v>
+        <v>0.1915795192190732</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.467243207253231</v>
+        <v>0.4591872898867959</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1571867995506536</v>
+        <v>0.1587367995506536</v>
       </c>
       <c r="C60">
-        <v>-3428.44204519693</v>
+        <v>-3581.23551587049</v>
       </c>
       <c r="D60">
-        <v>3019.103954803069</v>
+        <v>2978.09748412951</v>
       </c>
       <c r="E60">
-        <v>2999.046</v>
+        <v>3110.833</v>
       </c>
       <c r="F60">
-        <v>6483.646</v>
+        <v>6595.433</v>
       </c>
       <c r="G60">
         <v>36.1</v>
@@ -6207,37 +6207,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M60">
-        <v>1301.9161168</v>
+        <v>1324.3629464</v>
       </c>
       <c r="N60">
-        <v>-704.0927834666667</v>
+        <v>-726.5396130666667</v>
       </c>
       <c r="O60">
-        <v>-70.40927834666667</v>
+        <v>-72.65396130666667</v>
       </c>
       <c r="P60">
-        <v>-633.6835051200001</v>
+        <v>-653.88565176</v>
       </c>
       <c r="Q60">
-        <v>-627.6735051200001</v>
+        <v>-647.87565176</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1096920914371217</v>
+        <v>0.1112504351307101</v>
       </c>
       <c r="T60">
-        <v>1.28063135599992</v>
+        <v>1.311866267121869</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.0459187289886796</v>
+        <v>0.04514044544649859</v>
       </c>
       <c r="W60">
-        <v>0.1915795192190732</v>
+        <v>0.1917357985543431</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.459187289886796</v>
+        <v>0.4514044544649859</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1587367995506536</v>
+        <v>0.1602867995506536</v>
       </c>
       <c r="C61">
-        <v>-3581.23551587049</v>
+        <v>-3732.929986571304</v>
       </c>
       <c r="D61">
-        <v>2978.09748412951</v>
+        <v>2938.190013428697</v>
       </c>
       <c r="E61">
-        <v>3110.833</v>
+        <v>3222.62</v>
       </c>
       <c r="F61">
-        <v>6595.433</v>
+        <v>6707.22</v>
       </c>
       <c r="G61">
         <v>36.1</v>
@@ -6289,37 +6289,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M61">
-        <v>1324.3629464</v>
+        <v>1346.809776</v>
       </c>
       <c r="N61">
-        <v>-726.5396130666667</v>
+        <v>-748.9864426666667</v>
       </c>
       <c r="O61">
-        <v>-72.65396130666667</v>
+        <v>-74.89864426666666</v>
       </c>
       <c r="P61">
-        <v>-653.88565176</v>
+        <v>-674.0877984</v>
       </c>
       <c r="Q61">
-        <v>-647.87565176</v>
+        <v>-668.0777984</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1112504351307101</v>
+        <v>0.1128866960089778</v>
       </c>
       <c r="T61">
-        <v>1.311866267121869</v>
+        <v>1.344662923799916</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.04514044544649859</v>
+        <v>0.04438810468905695</v>
       </c>
       <c r="W61">
-        <v>0.1917357985543431</v>
+        <v>0.1918868685784374</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4514044544649859</v>
+        <v>0.4438810468905695</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1602867995506536</v>
+        <v>0.1618367995506536</v>
       </c>
       <c r="C62">
-        <v>-3732.929986571304</v>
+        <v>-3883.569053956633</v>
       </c>
       <c r="D62">
-        <v>2938.190013428697</v>
+        <v>2899.337946043368</v>
       </c>
       <c r="E62">
-        <v>3222.62</v>
+        <v>3334.407000000001</v>
       </c>
       <c r="F62">
-        <v>6707.22</v>
+        <v>6819.007000000001</v>
       </c>
       <c r="G62">
         <v>36.1</v>
@@ -6371,37 +6371,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M62">
-        <v>1346.809776</v>
+        <v>1369.2566056</v>
       </c>
       <c r="N62">
-        <v>-748.9864426666667</v>
+        <v>-771.4332722666667</v>
       </c>
       <c r="O62">
-        <v>-74.89864426666666</v>
+        <v>-77.14332722666667</v>
       </c>
       <c r="P62">
-        <v>-674.0877984</v>
+        <v>-694.28994504</v>
       </c>
       <c r="Q62">
-        <v>-668.0777984</v>
+        <v>-688.27994504</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1128866960089778</v>
+        <v>0.1146068677015157</v>
       </c>
       <c r="T62">
-        <v>1.344662923799916</v>
+        <v>1.379141460307606</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.04438810468905695</v>
+        <v>0.04366043084169536</v>
       </c>
       <c r="W62">
-        <v>0.1918868685784374</v>
+        <v>0.1920329854869876</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4438810468905695</v>
+        <v>0.4366043084169535</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1618367995506536</v>
+        <v>0.1633867995506535</v>
       </c>
       <c r="C63">
-        <v>-3883.569053956633</v>
+        <v>-4033.194038840515</v>
       </c>
       <c r="D63">
-        <v>2899.337946043368</v>
+        <v>2861.499961159486</v>
       </c>
       <c r="E63">
-        <v>3334.407000000001</v>
+        <v>3446.194000000001</v>
       </c>
       <c r="F63">
-        <v>6819.007000000001</v>
+        <v>6930.794000000001</v>
       </c>
       <c r="G63">
         <v>36.1</v>
@@ -6453,37 +6453,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M63">
-        <v>1369.2566056</v>
+        <v>1391.7034352</v>
       </c>
       <c r="N63">
-        <v>-771.4332722666667</v>
+        <v>-793.8801018666669</v>
       </c>
       <c r="O63">
-        <v>-77.14332722666667</v>
+        <v>-79.38801018666669</v>
       </c>
       <c r="P63">
-        <v>-694.28994504</v>
+        <v>-714.4920916800002</v>
       </c>
       <c r="Q63">
-        <v>-688.27994504</v>
+        <v>-708.4820916800002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1146068677015157</v>
+        <v>0.1164175747462924</v>
       </c>
       <c r="T63">
-        <v>1.379141460307606</v>
+        <v>1.41543465663149</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.04366043084169536</v>
+        <v>0.04295623034424866</v>
       </c>
       <c r="W63">
-        <v>0.1920329854869876</v>
+        <v>0.1921743889468749</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4366043084169535</v>
+        <v>0.4295623034424865</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1633867995506535</v>
+        <v>0.1649367995506535</v>
       </c>
       <c r="C64">
-        <v>-4033.194038840515</v>
+        <v>-4181.844132785793</v>
       </c>
       <c r="D64">
-        <v>2861.499961159486</v>
+        <v>2824.636867214208</v>
       </c>
       <c r="E64">
-        <v>3446.194000000001</v>
+        <v>3557.981</v>
       </c>
       <c r="F64">
-        <v>6930.794000000001</v>
+        <v>7042.581</v>
       </c>
       <c r="G64">
         <v>36.1</v>
@@ -6535,37 +6535,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M64">
-        <v>1391.7034352</v>
+        <v>1414.1502648</v>
       </c>
       <c r="N64">
-        <v>-793.8801018666669</v>
+        <v>-816.3269314666667</v>
       </c>
       <c r="O64">
-        <v>-79.38801018666669</v>
+        <v>-81.63269314666667</v>
       </c>
       <c r="P64">
-        <v>-714.4920916800002</v>
+        <v>-734.6942383200001</v>
       </c>
       <c r="Q64">
-        <v>-708.4820916800002</v>
+        <v>-728.6842383200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1164175747462924</v>
+        <v>0.1183261578475436</v>
       </c>
       <c r="T64">
-        <v>1.41543465663149</v>
+        <v>1.45368964735126</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.04295623034424866</v>
+        <v>0.04227438541814948</v>
       </c>
       <c r="W64">
-        <v>0.1921743889468749</v>
+        <v>0.1923113034080356</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4295623034424865</v>
+        <v>0.4227438541814947</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1649367995506535</v>
+        <v>0.1664867995506536</v>
       </c>
       <c r="C65">
-        <v>-4181.844132785793</v>
+        <v>-4329.556533509496</v>
       </c>
       <c r="D65">
-        <v>2824.636867214208</v>
+        <v>2788.711466490505</v>
       </c>
       <c r="E65">
-        <v>3557.981</v>
+        <v>3669.768</v>
       </c>
       <c r="F65">
-        <v>7042.581</v>
+        <v>7154.368</v>
       </c>
       <c r="G65">
         <v>36.1</v>
@@ -6617,37 +6617,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M65">
-        <v>1414.1502648</v>
+        <v>1436.5970944</v>
       </c>
       <c r="N65">
-        <v>-816.3269314666667</v>
+        <v>-838.7737610666667</v>
       </c>
       <c r="O65">
-        <v>-81.63269314666667</v>
+        <v>-83.87737610666667</v>
       </c>
       <c r="P65">
-        <v>-734.6942383200001</v>
+        <v>-754.89638496</v>
       </c>
       <c r="Q65">
-        <v>-728.6842383200001</v>
+        <v>-748.88638496</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1183261578475436</v>
+        <v>0.1203407733433087</v>
       </c>
       <c r="T65">
-        <v>1.45368964735126</v>
+        <v>1.49406991533324</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.04227438541814948</v>
+        <v>0.04161384814599089</v>
       </c>
       <c r="W65">
-        <v>0.1923113034080356</v>
+        <v>0.192443939292285</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4227438541814947</v>
+        <v>0.4161384814599088</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1664867995506536</v>
+        <v>0.1680367995506536</v>
       </c>
       <c r="C66">
-        <v>-4329.556533509496</v>
+        <v>-4476.366570084984</v>
       </c>
       <c r="D66">
-        <v>2788.711466490505</v>
+        <v>2753.688429915017</v>
       </c>
       <c r="E66">
-        <v>3669.768</v>
+        <v>3781.555000000001</v>
       </c>
       <c r="F66">
-        <v>7154.368</v>
+        <v>7266.155000000001</v>
       </c>
       <c r="G66">
         <v>36.1</v>
@@ -6699,37 +6699,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M66">
-        <v>1436.5970944</v>
+        <v>1459.043924</v>
       </c>
       <c r="N66">
-        <v>-838.7737610666667</v>
+        <v>-861.2205906666669</v>
       </c>
       <c r="O66">
-        <v>-83.87737610666667</v>
+        <v>-86.12205906666669</v>
       </c>
       <c r="P66">
-        <v>-754.89638496</v>
+        <v>-775.0985316000002</v>
       </c>
       <c r="Q66">
-        <v>-748.88638496</v>
+        <v>-769.0885316000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1203407733433087</v>
+        <v>0.1224705097245461</v>
       </c>
       <c r="T66">
-        <v>1.49406991533324</v>
+        <v>1.536757627199904</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.04161384814599089</v>
+        <v>0.04097363509759103</v>
       </c>
       <c r="W66">
-        <v>0.192443939292285</v>
+        <v>0.1925724940724037</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4161384814599088</v>
+        <v>0.4097363509759102</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1680367995506536</v>
+        <v>0.1695867995506535</v>
       </c>
       <c r="C67">
-        <v>-4476.366570084984</v>
+        <v>-4622.307818826748</v>
       </c>
       <c r="D67">
-        <v>2753.688429915017</v>
+        <v>2719.534181173253</v>
       </c>
       <c r="E67">
-        <v>3781.555000000001</v>
+        <v>3893.342000000001</v>
       </c>
       <c r="F67">
-        <v>7266.155000000001</v>
+        <v>7377.942000000001</v>
       </c>
       <c r="G67">
         <v>36.1</v>
@@ -6781,37 +6781,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M67">
-        <v>1459.043924</v>
+        <v>1481.4907536</v>
       </c>
       <c r="N67">
-        <v>-861.2205906666669</v>
+        <v>-883.6674202666669</v>
       </c>
       <c r="O67">
-        <v>-86.12205906666669</v>
+        <v>-88.3667420266667</v>
       </c>
       <c r="P67">
-        <v>-775.0985316000002</v>
+        <v>-795.3006782400003</v>
       </c>
       <c r="Q67">
-        <v>-769.0885316000002</v>
+        <v>-789.2906782400003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1224705097245461</v>
+        <v>0.1247255247164445</v>
       </c>
       <c r="T67">
-        <v>1.536757627199904</v>
+        <v>1.581956380941077</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.04097363509759103</v>
+        <v>0.04035282244459722</v>
       </c>
       <c r="W67">
-        <v>0.1925724940724037</v>
+        <v>0.1926971532531249</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4097363509759102</v>
+        <v>0.4035282244459721</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1695867995506535</v>
+        <v>0.1711367995506536</v>
       </c>
       <c r="C68">
-        <v>-4622.307818826748</v>
+        <v>-4767.412210656861</v>
       </c>
       <c r="D68">
-        <v>2719.534181173253</v>
+        <v>2686.21678934314</v>
       </c>
       <c r="E68">
-        <v>3893.342000000001</v>
+        <v>4005.129000000001</v>
       </c>
       <c r="F68">
-        <v>7377.942000000001</v>
+        <v>7489.729000000001</v>
       </c>
       <c r="G68">
         <v>36.1</v>
@@ -6863,37 +6863,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M68">
-        <v>1481.4907536</v>
+        <v>1503.9375832</v>
       </c>
       <c r="N68">
-        <v>-883.6674202666669</v>
+        <v>-906.1142498666669</v>
       </c>
       <c r="O68">
-        <v>-88.3667420266667</v>
+        <v>-90.61142498666669</v>
       </c>
       <c r="P68">
-        <v>-795.3006782400003</v>
+        <v>-815.5028248800002</v>
       </c>
       <c r="Q68">
-        <v>-789.2906782400003</v>
+        <v>-809.4928248800002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1247255247164445</v>
+        <v>0.1271172072836095</v>
       </c>
       <c r="T68">
-        <v>1.581956380941077</v>
+        <v>1.629894453090807</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.04035282244459722</v>
+        <v>0.03975054151258831</v>
       </c>
       <c r="W68">
-        <v>0.1926971532531249</v>
+        <v>0.1928180912642723</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4035282244459721</v>
+        <v>0.397505415125883</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1711367995506536</v>
+        <v>0.1726867995506536</v>
       </c>
       <c r="C69">
-        <v>-4767.412210656861</v>
+        <v>-4911.710130674803</v>
       </c>
       <c r="D69">
-        <v>2686.21678934314</v>
+        <v>2653.705869325199</v>
       </c>
       <c r="E69">
-        <v>4005.129000000001</v>
+        <v>4116.916000000001</v>
       </c>
       <c r="F69">
-        <v>7489.729000000001</v>
+        <v>7601.516000000001</v>
       </c>
       <c r="G69">
         <v>36.1</v>
@@ -6945,37 +6945,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M69">
-        <v>1503.9375832</v>
+        <v>1526.3844128</v>
       </c>
       <c r="N69">
-        <v>-906.1142498666669</v>
+        <v>-928.5610794666669</v>
       </c>
       <c r="O69">
-        <v>-90.61142498666669</v>
+        <v>-92.8561079466667</v>
       </c>
       <c r="P69">
-        <v>-815.5028248800002</v>
+        <v>-835.7049715200002</v>
       </c>
       <c r="Q69">
-        <v>-809.4928248800002</v>
+        <v>-829.6949715200002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1271172072836095</v>
+        <v>0.1296583700112223</v>
       </c>
       <c r="T69">
-        <v>1.629894453090807</v>
+        <v>1.680828654749895</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.03975054151258831</v>
+        <v>0.03916597472563848</v>
       </c>
       <c r="W69">
-        <v>0.1928180912642723</v>
+        <v>0.1929354722750918</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.397505415125883</v>
+        <v>0.3916597472563847</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1726867995506536</v>
+        <v>0.1742367995506535</v>
       </c>
       <c r="C70">
-        <v>-4911.710130674803</v>
+        <v>-5055.230510583246</v>
       </c>
       <c r="D70">
-        <v>2653.705869325199</v>
+        <v>2621.972489416755</v>
       </c>
       <c r="E70">
-        <v>4116.916000000001</v>
+        <v>4228.703000000001</v>
       </c>
       <c r="F70">
-        <v>7601.516000000001</v>
+        <v>7713.303000000001</v>
       </c>
       <c r="G70">
         <v>36.1</v>
@@ -7027,37 +7027,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M70">
-        <v>1526.3844128</v>
+        <v>1548.8312424</v>
       </c>
       <c r="N70">
-        <v>-928.5610794666669</v>
+        <v>-951.0079090666669</v>
       </c>
       <c r="O70">
-        <v>-92.8561079466667</v>
+        <v>-95.1007909066667</v>
       </c>
       <c r="P70">
-        <v>-835.7049715200002</v>
+        <v>-855.9071181600002</v>
       </c>
       <c r="Q70">
-        <v>-829.6949715200002</v>
+        <v>-849.8971181600002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1296583700112223</v>
+        <v>0.1323634787212617</v>
       </c>
       <c r="T70">
-        <v>1.680828654749895</v>
+        <v>1.735048933935376</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.03916597472563848</v>
+        <v>0.03859835190352778</v>
       </c>
       <c r="W70">
-        <v>0.1929354722750918</v>
+        <v>0.1930494509377716</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3916597472563847</v>
+        <v>0.3859835190352777</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1742367995506535</v>
+        <v>0.1757867995506536</v>
       </c>
       <c r="C71">
-        <v>-5055.230510583246</v>
+        <v>-5198.000914560787</v>
       </c>
       <c r="D71">
-        <v>2621.972489416755</v>
+        <v>2590.989085439213</v>
       </c>
       <c r="E71">
-        <v>4228.703000000001</v>
+        <v>4340.490000000002</v>
       </c>
       <c r="F71">
-        <v>7713.303000000001</v>
+        <v>7825.090000000001</v>
       </c>
       <c r="G71">
         <v>36.1</v>
@@ -7109,37 +7109,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M71">
-        <v>1548.8312424</v>
+        <v>1571.278072</v>
       </c>
       <c r="N71">
-        <v>-951.0079090666669</v>
+        <v>-973.4547386666669</v>
       </c>
       <c r="O71">
-        <v>-95.1007909066667</v>
+        <v>-97.34547386666669</v>
       </c>
       <c r="P71">
-        <v>-855.9071181600002</v>
+        <v>-876.1092648000002</v>
       </c>
       <c r="Q71">
-        <v>-849.8971181600002</v>
+        <v>-870.0992648000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1323634787212617</v>
+        <v>0.1352489280119704</v>
       </c>
       <c r="T71">
-        <v>1.735048933935376</v>
+        <v>1.792883898399888</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.03859835190352778</v>
+        <v>0.03804694687633452</v>
       </c>
       <c r="W71">
-        <v>0.1930494509377716</v>
+        <v>0.193160173067232</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3859835190352777</v>
+        <v>0.3804694687633452</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1757867995506536</v>
+        <v>0.1773367995506536</v>
       </c>
       <c r="C72">
-        <v>-5198.000914560787</v>
+        <v>-5340.047619117297</v>
       </c>
       <c r="D72">
-        <v>2590.989085439213</v>
+        <v>2560.729380882704</v>
       </c>
       <c r="E72">
-        <v>4340.490000000002</v>
+        <v>4452.277000000002</v>
       </c>
       <c r="F72">
-        <v>7825.090000000001</v>
+        <v>7936.877000000001</v>
       </c>
       <c r="G72">
         <v>36.1</v>
@@ -7191,37 +7191,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M72">
-        <v>1571.278072</v>
+        <v>1593.7249016</v>
       </c>
       <c r="N72">
-        <v>-973.4547386666669</v>
+        <v>-995.9015682666669</v>
       </c>
       <c r="O72">
-        <v>-97.34547386666669</v>
+        <v>-99.5901568266667</v>
       </c>
       <c r="P72">
-        <v>-876.1092648000002</v>
+        <v>-896.3114114400003</v>
       </c>
       <c r="Q72">
-        <v>-870.0992648000002</v>
+        <v>-890.3014114400003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1352489280119704</v>
+        <v>0.1383333738054867</v>
       </c>
       <c r="T72">
-        <v>1.792883898399888</v>
+        <v>1.854707481103333</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.03804694687633452</v>
+        <v>0.03751107438511855</v>
       </c>
       <c r="W72">
-        <v>0.193160173067232</v>
+        <v>0.1932677762634682</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3804694687633452</v>
+        <v>0.3751107438511854</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1773367995506536</v>
+        <v>0.1788867995506536</v>
       </c>
       <c r="C73">
-        <v>-5340.047619117297</v>
+        <v>-5481.395687418186</v>
       </c>
       <c r="D73">
-        <v>2560.729380882704</v>
+        <v>2531.168312581815</v>
       </c>
       <c r="E73">
-        <v>4452.277</v>
+        <v>4564.064</v>
       </c>
       <c r="F73">
-        <v>7936.877</v>
+        <v>8048.664000000001</v>
       </c>
       <c r="G73">
         <v>36.1</v>
@@ -7273,37 +7273,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M73">
-        <v>1593.7249016</v>
+        <v>1616.1717312</v>
       </c>
       <c r="N73">
-        <v>-995.9015682666667</v>
+        <v>-1018.348397866667</v>
       </c>
       <c r="O73">
-        <v>-99.59015682666667</v>
+        <v>-101.8348397866667</v>
       </c>
       <c r="P73">
-        <v>-896.31141144</v>
+        <v>-916.5135580800002</v>
       </c>
       <c r="Q73">
-        <v>-890.30141144</v>
+        <v>-910.5035580800002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1383333738054867</v>
+        <v>0.1416381371556826</v>
       </c>
       <c r="T73">
-        <v>1.854707481103332</v>
+        <v>1.92094703399988</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.03751107438511855</v>
+        <v>0.03699008724088079</v>
       </c>
       <c r="W73">
-        <v>0.1932677762634682</v>
+        <v>0.1933723904820311</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3751107438511855</v>
+        <v>0.3699008724088079</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1788867995506536</v>
+        <v>0.1804367995506535</v>
       </c>
       <c r="C74">
-        <v>-5481.395687418186</v>
+        <v>-5622.069038519414</v>
       </c>
       <c r="D74">
-        <v>2531.168312581815</v>
+        <v>2502.281961480586</v>
       </c>
       <c r="E74">
-        <v>4564.064</v>
+        <v>4675.851000000001</v>
       </c>
       <c r="F74">
-        <v>8048.664000000001</v>
+        <v>8160.451</v>
       </c>
       <c r="G74">
         <v>36.1</v>
@@ -7355,37 +7355,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M74">
-        <v>1616.1717312</v>
+        <v>1638.6185608</v>
       </c>
       <c r="N74">
-        <v>-1018.348397866667</v>
+        <v>-1040.795227466667</v>
       </c>
       <c r="O74">
-        <v>-101.8348397866667</v>
+        <v>-104.0795227466667</v>
       </c>
       <c r="P74">
-        <v>-916.5135580800002</v>
+        <v>-936.7157047200001</v>
       </c>
       <c r="Q74">
-        <v>-910.5035580800002</v>
+        <v>-930.7057047200001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1416381371556826</v>
+        <v>0.1451876977910782</v>
       </c>
       <c r="T74">
-        <v>1.92094703399988</v>
+        <v>1.992093220444319</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.03699008724088079</v>
+        <v>0.03648337371703311</v>
       </c>
       <c r="W74">
-        <v>0.1933723904820311</v>
+        <v>0.1934741385576197</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3699008724088079</v>
+        <v>0.364833737170331</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1804367995506535</v>
+        <v>0.1819867995506536</v>
       </c>
       <c r="C75">
-        <v>-5622.069038519414</v>
+        <v>-5762.090511915232</v>
       </c>
       <c r="D75">
-        <v>2502.281961480586</v>
+        <v>2474.047488084769</v>
       </c>
       <c r="E75">
-        <v>4675.851000000001</v>
+        <v>4787.638000000001</v>
       </c>
       <c r="F75">
-        <v>8160.451</v>
+        <v>8272.238000000001</v>
       </c>
       <c r="G75">
         <v>36.1</v>
@@ -7437,37 +7437,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M75">
-        <v>1638.6185608</v>
+        <v>1661.0653904</v>
       </c>
       <c r="N75">
-        <v>-1040.795227466667</v>
+        <v>-1063.242057066667</v>
       </c>
       <c r="O75">
-        <v>-104.0795227466667</v>
+        <v>-106.3242057066667</v>
       </c>
       <c r="P75">
-        <v>-936.7157047200001</v>
+        <v>-956.9178513600001</v>
       </c>
       <c r="Q75">
-        <v>-930.7057047200001</v>
+        <v>-950.9078513600001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1451876977910782</v>
+        <v>0.1490103015522736</v>
       </c>
       <c r="T75">
-        <v>1.992093220444319</v>
+        <v>2.068712190461409</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.03648337371703311</v>
+        <v>0.03599035515328941</v>
       </c>
       <c r="W75">
-        <v>0.1934741385576197</v>
+        <v>0.1935731366852195</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.364833737170331</v>
+        <v>0.3599035515328942</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1819867995506536</v>
+        <v>0.1835367995506536</v>
       </c>
       <c r="C76">
-        <v>-5762.090511915232</v>
+        <v>-5901.481927764733</v>
       </c>
       <c r="D76">
-        <v>2474.047488084769</v>
+        <v>2446.443072235269</v>
       </c>
       <c r="E76">
-        <v>4787.638000000001</v>
+        <v>4899.425000000001</v>
       </c>
       <c r="F76">
-        <v>8272.238000000001</v>
+        <v>8384.025000000001</v>
       </c>
       <c r="G76">
         <v>36.1</v>
@@ -7519,37 +7519,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M76">
-        <v>1661.0653904</v>
+        <v>1683.51222</v>
       </c>
       <c r="N76">
-        <v>-1063.242057066667</v>
+        <v>-1085.688886666667</v>
       </c>
       <c r="O76">
-        <v>-106.3242057066667</v>
+        <v>-108.5688886666667</v>
       </c>
       <c r="P76">
-        <v>-956.9178513600001</v>
+        <v>-977.1199980000001</v>
       </c>
       <c r="Q76">
-        <v>-950.9078513600001</v>
+        <v>-971.1099980000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1490103015522736</v>
+        <v>0.1531387136143645</v>
       </c>
       <c r="T76">
-        <v>2.068712190461409</v>
+        <v>2.151460678079865</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.03599035515328941</v>
+        <v>0.03551048375124555</v>
       </c>
       <c r="W76">
-        <v>0.1935731366852195</v>
+        <v>0.1936694948627499</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3599035515328942</v>
+        <v>0.3551048375124556</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1835367995506536</v>
+        <v>0.1850867995506535</v>
       </c>
       <c r="C77">
-        <v>-5901.481927764733</v>
+        <v>-6040.264143130987</v>
       </c>
       <c r="D77">
-        <v>2446.443072235269</v>
+        <v>2419.447856869013</v>
       </c>
       <c r="E77">
-        <v>4899.425000000001</v>
+        <v>5011.212</v>
       </c>
       <c r="F77">
-        <v>8384.025000000001</v>
+        <v>8495.812</v>
       </c>
       <c r="G77">
         <v>36.1</v>
@@ -7601,37 +7601,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M77">
-        <v>1683.51222</v>
+        <v>1705.9590496</v>
       </c>
       <c r="N77">
-        <v>-1085.688886666667</v>
+        <v>-1108.135716266667</v>
       </c>
       <c r="O77">
-        <v>-108.5688886666667</v>
+        <v>-110.8135716266667</v>
       </c>
       <c r="P77">
-        <v>-977.1199980000001</v>
+        <v>-997.3221446400001</v>
       </c>
       <c r="Q77">
-        <v>-971.1099980000001</v>
+        <v>-991.3121446400002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1531387136143645</v>
+        <v>0.1576111600149631</v>
       </c>
       <c r="T77">
-        <v>2.151460678079865</v>
+        <v>2.24110487299986</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.03551048375124555</v>
+        <v>0.03504324054399233</v>
       </c>
       <c r="W77">
-        <v>0.1936694948627499</v>
+        <v>0.1937633172987663</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3551048375124556</v>
+        <v>0.3504324054399232</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1850867995506535</v>
+        <v>0.1866367995506535</v>
       </c>
       <c r="C78">
-        <v>-6040.264143130987</v>
+        <v>-6178.457104537421</v>
       </c>
       <c r="D78">
-        <v>2419.447856869013</v>
+        <v>2393.041895462579</v>
       </c>
       <c r="E78">
-        <v>5011.212</v>
+        <v>5122.999</v>
       </c>
       <c r="F78">
-        <v>8495.812</v>
+        <v>8607.599</v>
       </c>
       <c r="G78">
         <v>36.1</v>
@@ -7683,37 +7683,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M78">
-        <v>1705.9590496</v>
+        <v>1728.4058792</v>
       </c>
       <c r="N78">
-        <v>-1108.135716266667</v>
+        <v>-1130.582545866667</v>
       </c>
       <c r="O78">
-        <v>-110.8135716266667</v>
+        <v>-113.0582545866667</v>
       </c>
       <c r="P78">
-        <v>-997.3221446400001</v>
+        <v>-1017.52429128</v>
       </c>
       <c r="Q78">
-        <v>-991.3121446400002</v>
+        <v>-1011.51429128</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1576111600149631</v>
+        <v>0.1624725147982223</v>
       </c>
       <c r="T78">
-        <v>2.24110487299986</v>
+        <v>2.338544215304201</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.03504324054399233</v>
+        <v>0.03458813352394048</v>
       </c>
       <c r="W78">
-        <v>0.1937633172987663</v>
+        <v>0.1938547027883928</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3504324054399232</v>
+        <v>0.3458813352394047</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1866367995506535</v>
+        <v>0.1881867995506535</v>
       </c>
       <c r="C79">
-        <v>-6178.457104537421</v>
+        <v>-6316.079897119712</v>
       </c>
       <c r="D79">
-        <v>2393.041895462579</v>
+        <v>2367.206102880289</v>
       </c>
       <c r="E79">
-        <v>5122.999</v>
+        <v>5234.786</v>
       </c>
       <c r="F79">
-        <v>8607.599</v>
+        <v>8719.386</v>
       </c>
       <c r="G79">
         <v>36.1</v>
@@ -7765,37 +7765,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M79">
-        <v>1728.4058792</v>
+        <v>1750.8527088</v>
       </c>
       <c r="N79">
-        <v>-1130.582545866667</v>
+        <v>-1153.029375466667</v>
       </c>
       <c r="O79">
-        <v>-113.0582545866667</v>
+        <v>-115.3029375466667</v>
       </c>
       <c r="P79">
-        <v>-1017.52429128</v>
+        <v>-1037.72643792</v>
       </c>
       <c r="Q79">
-        <v>-1011.51429128</v>
+        <v>-1031.71643792</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1624725147982223</v>
+        <v>0.1677758109254142</v>
       </c>
       <c r="T79">
-        <v>2.338544215304201</v>
+        <v>2.444841679636211</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.03458813352394048</v>
+        <v>0.03414469591465919</v>
       </c>
       <c r="W79">
-        <v>0.1938547027883928</v>
+        <v>0.1939437450603364</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3458813352394047</v>
+        <v>0.3414469591465918</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1881867995506535</v>
+        <v>0.1897367995506536</v>
       </c>
       <c r="C80">
-        <v>-6316.079897119712</v>
+        <v>-6453.150790627771</v>
       </c>
       <c r="D80">
-        <v>2367.206102880289</v>
+        <v>2341.92220937223</v>
       </c>
       <c r="E80">
-        <v>5234.786</v>
+        <v>5346.573</v>
       </c>
       <c r="F80">
-        <v>8719.386</v>
+        <v>8831.173000000001</v>
       </c>
       <c r="G80">
         <v>36.1</v>
@@ -7847,37 +7847,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M80">
-        <v>1750.8527088</v>
+        <v>1773.2995384</v>
       </c>
       <c r="N80">
-        <v>-1153.029375466667</v>
+        <v>-1175.476205066667</v>
       </c>
       <c r="O80">
-        <v>-115.3029375466667</v>
+        <v>-117.5476205066667</v>
       </c>
       <c r="P80">
-        <v>-1037.72643792</v>
+        <v>-1057.92858456</v>
       </c>
       <c r="Q80">
-        <v>-1031.71643792</v>
+        <v>-1051.91858456</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1677758109254142</v>
+        <v>0.1735841828742435</v>
       </c>
       <c r="T80">
-        <v>2.444841679636211</v>
+        <v>2.56126271199984</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.03414469591465919</v>
+        <v>0.0337124845739673</v>
       </c>
       <c r="W80">
-        <v>0.1939437450603364</v>
+        <v>0.1940305330975474</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3414469591465918</v>
+        <v>0.3371248457396731</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1897367995506536</v>
+        <v>0.1912867995506536</v>
       </c>
       <c r="C81">
-        <v>-6453.150790627771</v>
+        <v>-6589.687282510836</v>
       </c>
       <c r="D81">
-        <v>2341.92220937223</v>
+        <v>2317.172717489165</v>
       </c>
       <c r="E81">
-        <v>5346.573</v>
+        <v>5458.360000000001</v>
       </c>
       <c r="F81">
-        <v>8831.173000000001</v>
+        <v>8942.960000000001</v>
       </c>
       <c r="G81">
         <v>36.1</v>
@@ -7929,37 +7929,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M81">
-        <v>1773.2995384</v>
+        <v>1795.746368</v>
       </c>
       <c r="N81">
-        <v>-1175.476205066667</v>
+        <v>-1197.923034666667</v>
       </c>
       <c r="O81">
-        <v>-117.5476205066667</v>
+        <v>-119.7923034666667</v>
       </c>
       <c r="P81">
-        <v>-1057.92858456</v>
+        <v>-1078.1307312</v>
       </c>
       <c r="Q81">
-        <v>-1051.91858456</v>
+        <v>-1072.1207312</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1735841828742435</v>
+        <v>0.1799733920179557</v>
       </c>
       <c r="T81">
-        <v>2.56126271199984</v>
+        <v>2.689325847599832</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.0337124845739673</v>
+        <v>0.03329107851679271</v>
       </c>
       <c r="W81">
-        <v>0.1940305330975474</v>
+        <v>0.194115151433828</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3371248457396731</v>
+        <v>0.3329107851679272</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1912867995506536</v>
+        <v>0.1928367995506536</v>
       </c>
       <c r="C82">
-        <v>-6589.687282510836</v>
+        <v>-6725.706138299172</v>
       </c>
       <c r="D82">
-        <v>2317.172717489165</v>
+        <v>2292.940861700829</v>
       </c>
       <c r="E82">
-        <v>5458.360000000001</v>
+        <v>5570.147000000001</v>
       </c>
       <c r="F82">
-        <v>8942.960000000001</v>
+        <v>9054.747000000001</v>
       </c>
       <c r="G82">
         <v>36.1</v>
@@ -8011,37 +8011,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M82">
-        <v>1795.746368</v>
+        <v>1818.1931976</v>
       </c>
       <c r="N82">
-        <v>-1197.923034666667</v>
+        <v>-1220.369864266667</v>
       </c>
       <c r="O82">
-        <v>-119.7923034666667</v>
+        <v>-122.0369864266667</v>
       </c>
       <c r="P82">
-        <v>-1078.1307312</v>
+        <v>-1098.33287784</v>
       </c>
       <c r="Q82">
-        <v>-1072.1207312</v>
+        <v>-1092.32287784</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1799733920179557</v>
+        <v>0.1870351494925849</v>
       </c>
       <c r="T82">
-        <v>2.689325847599832</v>
+        <v>2.830869313262981</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.03329107851679271</v>
+        <v>0.03288007754744959</v>
       </c>
       <c r="W82">
-        <v>0.194115151433828</v>
+        <v>0.1941976804284721</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3329107851679272</v>
+        <v>0.3288007754744959</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1928367995506536</v>
+        <v>0.1943867995506536</v>
       </c>
       <c r="C83">
-        <v>-6725.706138299172</v>
+        <v>-6861.223429478259</v>
       </c>
       <c r="D83">
-        <v>2292.940861700829</v>
+        <v>2269.210570521742</v>
       </c>
       <c r="E83">
-        <v>5570.147000000001</v>
+        <v>5681.934000000001</v>
       </c>
       <c r="F83">
-        <v>9054.747000000001</v>
+        <v>9166.534000000001</v>
       </c>
       <c r="G83">
         <v>36.1</v>
@@ -8093,37 +8093,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M83">
-        <v>1818.1931976</v>
+        <v>1840.6400272</v>
       </c>
       <c r="N83">
-        <v>-1220.369864266667</v>
+        <v>-1242.816693866667</v>
       </c>
       <c r="O83">
-        <v>-122.0369864266667</v>
+        <v>-124.2816693866667</v>
       </c>
       <c r="P83">
-        <v>-1098.33287784</v>
+        <v>-1118.53502448</v>
       </c>
       <c r="Q83">
-        <v>-1092.32287784</v>
+        <v>-1112.52502448</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1870351494925849</v>
+        <v>0.1948815466866174</v>
       </c>
       <c r="T83">
-        <v>2.830869313262981</v>
+        <v>2.98813983066648</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.03288007754744959</v>
+        <v>0.03247910099199288</v>
       </c>
       <c r="W83">
-        <v>0.1941976804284721</v>
+        <v>0.1942781965208078</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3288007754744959</v>
+        <v>0.3247910099199289</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1943867995506536</v>
+        <v>0.1959367995506536</v>
       </c>
       <c r="C84">
-        <v>-6861.223429478259</v>
+        <v>-6996.254569035227</v>
       </c>
       <c r="D84">
-        <v>2269.210570521742</v>
+        <v>2245.966430964775</v>
       </c>
       <c r="E84">
-        <v>5681.934000000001</v>
+        <v>5793.721000000001</v>
       </c>
       <c r="F84">
-        <v>9166.534000000001</v>
+        <v>9278.321000000002</v>
       </c>
       <c r="G84">
         <v>36.1</v>
@@ -8175,37 +8175,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M84">
-        <v>1840.6400272</v>
+        <v>1863.0868568</v>
       </c>
       <c r="N84">
-        <v>-1242.816693866667</v>
+        <v>-1265.263523466667</v>
       </c>
       <c r="O84">
-        <v>-124.2816693866667</v>
+        <v>-126.5263523466667</v>
       </c>
       <c r="P84">
-        <v>-1118.53502448</v>
+        <v>-1138.73717112</v>
       </c>
       <c r="Q84">
-        <v>-1112.52502448</v>
+        <v>-1132.72717112</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1948815466866174</v>
+        <v>0.2036510494328891</v>
       </c>
       <c r="T84">
-        <v>2.98813983066648</v>
+        <v>3.163912761882157</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.03247910099199288</v>
+        <v>0.03208778652220984</v>
       </c>
       <c r="W84">
-        <v>0.1942781965208078</v>
+        <v>0.1943567724663403</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3247910099199289</v>
+        <v>0.3208778652220984</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1959367995506536</v>
+        <v>0.1974867995506536</v>
       </c>
       <c r="C85">
-        <v>-6996.254569035227</v>
+        <v>-7130.814344842787</v>
       </c>
       <c r="D85">
-        <v>2245.966430964775</v>
+        <v>2223.193655157214</v>
       </c>
       <c r="E85">
-        <v>5793.721000000001</v>
+        <v>5905.508000000002</v>
       </c>
       <c r="F85">
-        <v>9278.321000000002</v>
+        <v>9390.108000000002</v>
       </c>
       <c r="G85">
         <v>36.1</v>
@@ -8257,37 +8257,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M85">
-        <v>1863.0868568</v>
+        <v>1885.533686400001</v>
       </c>
       <c r="N85">
-        <v>-1265.263523466667</v>
+        <v>-1287.710353066667</v>
       </c>
       <c r="O85">
-        <v>-126.5263523466667</v>
+        <v>-128.7710353066667</v>
       </c>
       <c r="P85">
-        <v>-1138.73717112</v>
+        <v>-1158.93931776</v>
       </c>
       <c r="Q85">
-        <v>-1132.72717112</v>
+        <v>-1152.92931776</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2036510494328891</v>
+        <v>0.2135167400224447</v>
       </c>
       <c r="T85">
-        <v>3.163912761882157</v>
+        <v>3.361657309499792</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.03208778652220984</v>
+        <v>0.03170578906361209</v>
       </c>
       <c r="W85">
-        <v>0.1943567724663403</v>
+        <v>0.1944334775560267</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3208778652220984</v>
+        <v>0.3170578906361209</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1974867995506535</v>
+        <v>0.1990367995506536</v>
       </c>
       <c r="C86">
-        <v>-7130.814344842785</v>
+        <v>-7264.916951032585</v>
       </c>
       <c r="D86">
-        <v>2223.193655157214</v>
+        <v>2200.878048967416</v>
       </c>
       <c r="E86">
-        <v>5905.508</v>
+        <v>6017.295</v>
       </c>
       <c r="F86">
-        <v>9390.108</v>
+        <v>9501.895</v>
       </c>
       <c r="G86">
         <v>36.1</v>
@@ -8339,37 +8339,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M86">
-        <v>1885.5336864</v>
+        <v>1907.980516</v>
       </c>
       <c r="N86">
-        <v>-1287.710353066667</v>
+        <v>-1310.157182666667</v>
       </c>
       <c r="O86">
-        <v>-128.7710353066667</v>
+        <v>-131.0157182666667</v>
       </c>
       <c r="P86">
-        <v>-1158.93931776</v>
+        <v>-1179.1414644</v>
       </c>
       <c r="Q86">
-        <v>-1152.92931776</v>
+        <v>-1173.1314644</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2135167400224445</v>
+        <v>0.2246978560239409</v>
       </c>
       <c r="T86">
-        <v>3.361657309499789</v>
+        <v>3.585767796799776</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.03170578906361211</v>
+        <v>0.03133277978051079</v>
       </c>
       <c r="W86">
-        <v>0.1944334775560267</v>
+        <v>0.1945083778200734</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.317057890636121</v>
+        <v>0.3133277978051078</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1990367995506536</v>
+        <v>0.2005867995506536</v>
       </c>
       <c r="C87">
-        <v>-7264.916951032585</v>
+        <v>-7398.57601749784</v>
       </c>
       <c r="D87">
-        <v>2200.878048967416</v>
+        <v>2179.005982502161</v>
       </c>
       <c r="E87">
-        <v>6017.295</v>
+        <v>6129.082</v>
       </c>
       <c r="F87">
-        <v>9501.895</v>
+        <v>9613.682000000001</v>
       </c>
       <c r="G87">
         <v>36.1</v>
@@ -8421,37 +8421,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M87">
-        <v>1907.980516</v>
+        <v>1930.4273456</v>
       </c>
       <c r="N87">
-        <v>-1310.157182666667</v>
+        <v>-1332.604012266667</v>
       </c>
       <c r="O87">
-        <v>-131.0157182666667</v>
+        <v>-133.2604012266667</v>
       </c>
       <c r="P87">
-        <v>-1179.1414644</v>
+        <v>-1199.34361104</v>
       </c>
       <c r="Q87">
-        <v>-1173.1314644</v>
+        <v>-1193.33361104</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2246978560239409</v>
+        <v>0.2374762743113652</v>
       </c>
       <c r="T87">
-        <v>3.585767796799776</v>
+        <v>3.841894067999759</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.03133277978051079</v>
+        <v>0.03096844513190019</v>
       </c>
       <c r="W87">
-        <v>0.1945083778200734</v>
+        <v>0.1945815362175145</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3133277978051078</v>
+        <v>0.309684451319002</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2005867995506536</v>
+        <v>0.2021367995506536</v>
       </c>
       <c r="C88">
-        <v>-7398.57601749784</v>
+        <v>-7531.804637654139</v>
       </c>
       <c r="D88">
-        <v>2179.005982502161</v>
+        <v>2157.564362345862</v>
       </c>
       <c r="E88">
-        <v>6129.082</v>
+        <v>6240.869000000001</v>
       </c>
       <c r="F88">
-        <v>9613.682000000001</v>
+        <v>9725.469000000001</v>
       </c>
       <c r="G88">
         <v>36.1</v>
@@ -8503,37 +8503,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M88">
-        <v>1930.4273456</v>
+        <v>1952.8741752</v>
       </c>
       <c r="N88">
-        <v>-1332.604012266667</v>
+        <v>-1355.050841866667</v>
       </c>
       <c r="O88">
-        <v>-133.2604012266667</v>
+        <v>-135.5050841866667</v>
       </c>
       <c r="P88">
-        <v>-1199.34361104</v>
+        <v>-1219.54575768</v>
       </c>
       <c r="Q88">
-        <v>-1193.33361104</v>
+        <v>-1213.53575768</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2374762743113652</v>
+        <v>0.2522206031045471</v>
       </c>
       <c r="T88">
-        <v>3.841894067999759</v>
+        <v>4.137424380922818</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.03096844513190019</v>
+        <v>0.03061248599245307</v>
       </c>
       <c r="W88">
-        <v>0.1945815362175145</v>
+        <v>0.1946530128127154</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.309684451319002</v>
+        <v>0.3061248599245306</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2021367995506536</v>
+        <v>0.2036867995506536</v>
       </c>
       <c r="C89">
-        <v>-7531.804637654139</v>
+        <v>-7664.615394577184</v>
       </c>
       <c r="D89">
-        <v>2157.564362345862</v>
+        <v>2136.540605422818</v>
       </c>
       <c r="E89">
-        <v>6240.869000000001</v>
+        <v>6352.656000000001</v>
       </c>
       <c r="F89">
-        <v>9725.469000000001</v>
+        <v>9837.256000000001</v>
       </c>
       <c r="G89">
         <v>36.1</v>
@@ -8585,37 +8585,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M89">
-        <v>1952.8741752</v>
+        <v>1975.3210048</v>
       </c>
       <c r="N89">
-        <v>-1355.050841866667</v>
+        <v>-1377.497671466667</v>
       </c>
       <c r="O89">
-        <v>-135.5050841866667</v>
+        <v>-137.7497671466667</v>
       </c>
       <c r="P89">
-        <v>-1219.54575768</v>
+        <v>-1239.74790432</v>
       </c>
       <c r="Q89">
-        <v>-1213.53575768</v>
+        <v>-1233.73790432</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2522206031045471</v>
+        <v>0.2694223200299261</v>
       </c>
       <c r="T89">
-        <v>4.137424380922818</v>
+        <v>4.48220974599972</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.03061248599245307</v>
+        <v>0.03026461683344792</v>
       </c>
       <c r="W89">
-        <v>0.1946530128127154</v>
+        <v>0.1947228649398437</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3061248599245306</v>
+        <v>0.3026461683344792</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2036867995506536</v>
+        <v>0.2052367995506535</v>
       </c>
       <c r="C90">
-        <v>-7664.615394577184</v>
+        <v>-7797.020385627138</v>
       </c>
       <c r="D90">
-        <v>2136.540605422818</v>
+        <v>2115.922614372863</v>
       </c>
       <c r="E90">
-        <v>6352.656000000001</v>
+        <v>6464.443000000001</v>
       </c>
       <c r="F90">
-        <v>9837.256000000001</v>
+        <v>9949.043000000001</v>
       </c>
       <c r="G90">
         <v>36.1</v>
@@ -8667,37 +8667,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M90">
-        <v>1975.3210048</v>
+        <v>1997.7678344</v>
       </c>
       <c r="N90">
-        <v>-1377.497671466667</v>
+        <v>-1399.944501066667</v>
       </c>
       <c r="O90">
-        <v>-137.7497671466667</v>
+        <v>-139.9944501066667</v>
       </c>
       <c r="P90">
-        <v>-1239.74790432</v>
+        <v>-1259.95005096</v>
       </c>
       <c r="Q90">
-        <v>-1233.73790432</v>
+        <v>-1253.94005096</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2694223200299261</v>
+        <v>0.2897516218508284</v>
       </c>
       <c r="T90">
-        <v>4.48220974599972</v>
+        <v>4.889683359272421</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.03026461683344792</v>
+        <v>0.02992456495891479</v>
       </c>
       <c r="W90">
-        <v>0.1947228649398437</v>
+        <v>0.1947911473562499</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3026461683344792</v>
+        <v>0.299245649589148</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2052367995506535</v>
+        <v>0.2067867995506535</v>
       </c>
       <c r="C91">
-        <v>-7797.020385627138</v>
+        <v>-7929.031245660828</v>
       </c>
       <c r="D91">
-        <v>2115.922614372863</v>
+        <v>2095.698754339174</v>
       </c>
       <c r="E91">
-        <v>6464.443000000001</v>
+        <v>6576.230000000001</v>
       </c>
       <c r="F91">
-        <v>9949.043000000001</v>
+        <v>10060.83</v>
       </c>
       <c r="G91">
         <v>36.1</v>
@@ -8749,37 +8749,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M91">
-        <v>1997.7678344</v>
+        <v>2020.214664</v>
       </c>
       <c r="N91">
-        <v>-1399.944501066667</v>
+        <v>-1422.391330666667</v>
       </c>
       <c r="O91">
-        <v>-139.9944501066667</v>
+        <v>-142.2391330666667</v>
       </c>
       <c r="P91">
-        <v>-1259.95005096</v>
+        <v>-1280.1521976</v>
       </c>
       <c r="Q91">
-        <v>-1253.94005096</v>
+        <v>-1274.1421976</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2897516218508284</v>
+        <v>0.3141467840359113</v>
       </c>
       <c r="T91">
-        <v>4.889683359272421</v>
+        <v>5.378651695199664</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.02992456495891479</v>
+        <v>0.02959206979270463</v>
       </c>
       <c r="W91">
-        <v>0.1947911473562499</v>
+        <v>0.1948579123856249</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.299245649589148</v>
+        <v>0.2959206979270463</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2067867995506535</v>
+        <v>0.2083367995506535</v>
       </c>
       <c r="C92">
-        <v>-7929.031245660828</v>
+        <v>-8060.659168925373</v>
       </c>
       <c r="D92">
-        <v>2095.698754339174</v>
+        <v>2075.857831074627</v>
       </c>
       <c r="E92">
-        <v>6576.230000000001</v>
+        <v>6688.017</v>
       </c>
       <c r="F92">
-        <v>10060.83</v>
+        <v>10172.617</v>
       </c>
       <c r="G92">
         <v>36.1</v>
@@ -8831,37 +8831,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M92">
-        <v>2020.214664</v>
+        <v>2042.6614936</v>
       </c>
       <c r="N92">
-        <v>-1422.391330666667</v>
+        <v>-1444.838160266667</v>
       </c>
       <c r="O92">
-        <v>-142.2391330666667</v>
+        <v>-144.4838160266667</v>
       </c>
       <c r="P92">
-        <v>-1280.1521976</v>
+        <v>-1300.35434424</v>
       </c>
       <c r="Q92">
-        <v>-1274.1421976</v>
+        <v>-1294.34434424</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3141467840359113</v>
+        <v>0.3439630933732348</v>
       </c>
       <c r="T92">
-        <v>5.378651695199664</v>
+        <v>5.976279661332961</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.02959206979270463</v>
+        <v>0.02926688221256502</v>
       </c>
       <c r="W92">
-        <v>0.1948579123856249</v>
+        <v>0.1949232100517169</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2959206979270463</v>
+        <v>0.2926688221256502</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2083367995506535</v>
+        <v>0.2098867995506536</v>
       </c>
       <c r="C93">
-        <v>-8060.659168925373</v>
+        <v>-8191.914929719836</v>
       </c>
       <c r="D93">
-        <v>2075.857831074627</v>
+        <v>2056.389070280165</v>
       </c>
       <c r="E93">
-        <v>6688.017</v>
+        <v>6799.804</v>
       </c>
       <c r="F93">
-        <v>10172.617</v>
+        <v>10284.404</v>
       </c>
       <c r="G93">
         <v>36.1</v>
@@ -8913,37 +8913,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M93">
-        <v>2042.6614936</v>
+        <v>2065.1083232</v>
       </c>
       <c r="N93">
-        <v>-1444.838160266667</v>
+        <v>-1467.284989866667</v>
       </c>
       <c r="O93">
-        <v>-144.4838160266667</v>
+        <v>-146.7284989866667</v>
       </c>
       <c r="P93">
-        <v>-1300.35434424</v>
+        <v>-1320.55649088</v>
       </c>
       <c r="Q93">
-        <v>-1294.34434424</v>
+        <v>-1314.54649088</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3439630933732348</v>
+        <v>0.3812334800448893</v>
       </c>
       <c r="T93">
-        <v>5.976279661332961</v>
+        <v>6.723314618999583</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.02926688221256502</v>
+        <v>0.02894876392764583</v>
       </c>
       <c r="W93">
-        <v>0.1949232100517169</v>
+        <v>0.1949870882033287</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2926688221256502</v>
+        <v>0.2894876392764583</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2098867995506536</v>
+        <v>0.2114367995506536</v>
       </c>
       <c r="C94">
-        <v>-8191.914929719836</v>
+        <v>-8322.808901904978</v>
       </c>
       <c r="D94">
-        <v>2056.389070280165</v>
+        <v>2037.282098095022</v>
       </c>
       <c r="E94">
-        <v>6799.804</v>
+        <v>6911.591</v>
       </c>
       <c r="F94">
-        <v>10284.404</v>
+        <v>10396.191</v>
       </c>
       <c r="G94">
         <v>36.1</v>
@@ -8995,37 +8995,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M94">
-        <v>2065.1083232</v>
+        <v>2087.5551528</v>
       </c>
       <c r="N94">
-        <v>-1467.284989866667</v>
+        <v>-1489.731819466667</v>
       </c>
       <c r="O94">
-        <v>-146.7284989866667</v>
+        <v>-148.9731819466667</v>
       </c>
       <c r="P94">
-        <v>-1320.55649088</v>
+        <v>-1340.75863752</v>
       </c>
       <c r="Q94">
-        <v>-1314.54649088</v>
+        <v>-1334.74863752</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3812334800448893</v>
+        <v>0.4291525486227307</v>
       </c>
       <c r="T94">
-        <v>6.723314618999583</v>
+        <v>7.683788135999525</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.02894876392764583</v>
+        <v>0.02863748689616577</v>
       </c>
       <c r="W94">
-        <v>0.1949870882033287</v>
+        <v>0.1950495926312499</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2894876392764583</v>
+        <v>0.2863748689616576</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2114367995506536</v>
+        <v>0.2129867995506536</v>
       </c>
       <c r="C95">
-        <v>-8322.808901904978</v>
+        <v>-8453.351077335403</v>
       </c>
       <c r="D95">
-        <v>2037.282098095022</v>
+        <v>2018.526922664598</v>
       </c>
       <c r="E95">
-        <v>6911.591</v>
+        <v>7023.378000000001</v>
       </c>
       <c r="F95">
-        <v>10396.191</v>
+        <v>10507.978</v>
       </c>
       <c r="G95">
         <v>36.1</v>
@@ -9077,37 +9077,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M95">
-        <v>2087.5551528</v>
+        <v>2110.0019824</v>
       </c>
       <c r="N95">
-        <v>-1489.731819466667</v>
+        <v>-1512.178649066667</v>
       </c>
       <c r="O95">
-        <v>-148.9731819466667</v>
+        <v>-151.2178649066667</v>
       </c>
       <c r="P95">
-        <v>-1340.75863752</v>
+        <v>-1360.96078416</v>
       </c>
       <c r="Q95">
-        <v>-1334.74863752</v>
+        <v>-1354.95078416</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4291525486227307</v>
+        <v>0.4930446400598525</v>
       </c>
       <c r="T95">
-        <v>7.683788135999525</v>
+        <v>8.964419491999447</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.02863748689616577</v>
+        <v>0.02833283278024911</v>
       </c>
       <c r="W95">
-        <v>0.1950495926312499</v>
+        <v>0.195110767177726</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2863748689616576</v>
+        <v>0.2833283278024911</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2129867995506536</v>
+        <v>0.2145367995506536</v>
       </c>
       <c r="C96">
-        <v>-8453.351077335403</v>
+        <v>-8583.551083282857</v>
       </c>
       <c r="D96">
-        <v>2018.526922664598</v>
+        <v>2000.113916717144</v>
       </c>
       <c r="E96">
-        <v>7023.378000000001</v>
+        <v>7135.165000000001</v>
       </c>
       <c r="F96">
-        <v>10507.978</v>
+        <v>10619.765</v>
       </c>
       <c r="G96">
         <v>36.1</v>
@@ -9159,37 +9159,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M96">
-        <v>2110.0019824</v>
+        <v>2132.448812</v>
       </c>
       <c r="N96">
-        <v>-1512.178649066667</v>
+        <v>-1534.625478666667</v>
       </c>
       <c r="O96">
-        <v>-151.2178649066667</v>
+        <v>-153.4625478666667</v>
       </c>
       <c r="P96">
-        <v>-1360.96078416</v>
+        <v>-1381.1629308</v>
       </c>
       <c r="Q96">
-        <v>-1354.95078416</v>
+        <v>-1375.1529308</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4930446400598525</v>
+        <v>0.5824935680718233</v>
       </c>
       <c r="T96">
-        <v>8.964419491999447</v>
+        <v>10.75730339039934</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.02833283278024911</v>
+        <v>0.02803459243519386</v>
       </c>
       <c r="W96">
-        <v>0.195110767177726</v>
+        <v>0.1951706538390131</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2833283278024911</v>
+        <v>0.2803459243519385</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2145367995506536</v>
+        <v>0.2160867995506536</v>
       </c>
       <c r="C97">
-        <v>-8583.551083282857</v>
+        <v>-8713.41819891454</v>
       </c>
       <c r="D97">
-        <v>2000.113916717144</v>
+        <v>1982.033801085462</v>
       </c>
       <c r="E97">
-        <v>7135.165000000001</v>
+        <v>7246.952000000001</v>
       </c>
       <c r="F97">
-        <v>10619.765</v>
+        <v>10731.552</v>
       </c>
       <c r="G97">
         <v>36.1</v>
@@ -9241,37 +9241,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M97">
-        <v>2132.448812</v>
+        <v>2154.895641600001</v>
       </c>
       <c r="N97">
-        <v>-1534.625478666667</v>
+        <v>-1557.072308266667</v>
       </c>
       <c r="O97">
-        <v>-153.4625478666667</v>
+        <v>-155.7072308266667</v>
       </c>
       <c r="P97">
-        <v>-1381.1629308</v>
+        <v>-1401.365077440001</v>
       </c>
       <c r="Q97">
-        <v>-1375.1529308</v>
+        <v>-1395.355077440001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5824935680718233</v>
+        <v>0.7166669600897795</v>
       </c>
       <c r="T97">
-        <v>10.75730339039934</v>
+        <v>13.44662923799918</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.02803459243519386</v>
+        <v>0.02774256543066059</v>
       </c>
       <c r="W97">
-        <v>0.1951706538390131</v>
+        <v>0.1952292928615234</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2803459243519385</v>
+        <v>0.2774256543066058</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2160867995506536</v>
+        <v>0.2176367995506535</v>
       </c>
       <c r="C98">
-        <v>-8713.418198914538</v>
+        <v>-8842.961370885685</v>
       </c>
       <c r="D98">
-        <v>1982.033801085462</v>
+        <v>1964.277629114315</v>
       </c>
       <c r="E98">
-        <v>7246.951999999999</v>
+        <v>7358.739</v>
       </c>
       <c r="F98">
-        <v>10731.552</v>
+        <v>10843.339</v>
       </c>
       <c r="G98">
         <v>36.1</v>
@@ -9323,37 +9323,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M98">
-        <v>2154.8956416</v>
+        <v>2177.3424712</v>
       </c>
       <c r="N98">
-        <v>-1557.072308266667</v>
+        <v>-1579.519137866667</v>
       </c>
       <c r="O98">
-        <v>-155.7072308266667</v>
+        <v>-157.9519137866667</v>
       </c>
       <c r="P98">
-        <v>-1401.36507744</v>
+        <v>-1421.56722408</v>
       </c>
       <c r="Q98">
-        <v>-1395.35507744</v>
+        <v>-1415.55722408</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7166669600897776</v>
+        <v>0.9402892801197035</v>
       </c>
       <c r="T98">
-        <v>13.44662923799915</v>
+        <v>17.92883898399886</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.02774256543066059</v>
+        <v>0.02745655960147853</v>
       </c>
       <c r="W98">
-        <v>0.1952292928615234</v>
+        <v>0.1952867228320231</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2774256543066058</v>
+        <v>0.2745655960147851</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2176367995506535</v>
+        <v>0.2191867995506536</v>
       </c>
       <c r="C99">
-        <v>-8842.961370885685</v>
+        <v>-8972.189228101466</v>
       </c>
       <c r="D99">
-        <v>1964.277629114315</v>
+        <v>1946.836771898533</v>
       </c>
       <c r="E99">
-        <v>7358.739</v>
+        <v>7470.526</v>
       </c>
       <c r="F99">
-        <v>10843.339</v>
+        <v>10955.126</v>
       </c>
       <c r="G99">
         <v>36.1</v>
@@ -9405,37 +9405,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M99">
-        <v>2177.3424712</v>
+        <v>2199.7893008</v>
       </c>
       <c r="N99">
-        <v>-1579.519137866667</v>
+        <v>-1601.965967466667</v>
       </c>
       <c r="O99">
-        <v>-157.9519137866667</v>
+        <v>-160.1965967466667</v>
       </c>
       <c r="P99">
-        <v>-1421.56722408</v>
+        <v>-1441.76937072</v>
       </c>
       <c r="Q99">
-        <v>-1415.55722408</v>
+        <v>-1435.75937072</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9402892801197035</v>
+        <v>1.387533920179555</v>
       </c>
       <c r="T99">
-        <v>17.92883898399886</v>
+        <v>26.89325847599829</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.02745655960147853</v>
+        <v>0.02717639062595324</v>
       </c>
       <c r="W99">
-        <v>0.1952867228320231</v>
+        <v>0.1953429807623086</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2745655960147851</v>
+        <v>0.2717639062595323</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2191867995506536</v>
+        <v>0.2207367995506535</v>
       </c>
       <c r="C100">
-        <v>-8972.189228101466</v>
+        <v>-9101.110095699378</v>
       </c>
       <c r="D100">
-        <v>1946.836771898533</v>
+        <v>1929.702904300623</v>
       </c>
       <c r="E100">
-        <v>7470.526</v>
+        <v>7582.313</v>
       </c>
       <c r="F100">
-        <v>10955.126</v>
+        <v>11066.913</v>
       </c>
       <c r="G100">
         <v>36.1</v>
@@ -9487,37 +9487,37 @@
         <v>597.8233333333334</v>
       </c>
       <c r="M100">
-        <v>2199.7893008</v>
+        <v>2222.2361304</v>
       </c>
       <c r="N100">
-        <v>-1601.965967466667</v>
+        <v>-1624.412797066667</v>
       </c>
       <c r="O100">
-        <v>-160.1965967466667</v>
+        <v>-162.4412797066667</v>
       </c>
       <c r="P100">
-        <v>-1441.76937072</v>
+        <v>-1461.97151736</v>
       </c>
       <c r="Q100">
-        <v>-1435.75937072</v>
+        <v>-1455.96151736</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.387533920179555</v>
+        <v>2.72926784035911</v>
       </c>
       <c r="T100">
-        <v>26.89325847599829</v>
+        <v>53.78651695199659</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.02717639062595324</v>
+        <v>0.02690188162973148</v>
       </c>
       <c r="W100">
-        <v>0.1953429807623086</v>
+        <v>0.1953981021687499</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2717639062595323</v>
+        <v>0.2690188162973147</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2207367995506535</v>
-      </c>
-      <c r="C101">
-        <v>-9101.110095699378</v>
-      </c>
-      <c r="D101">
-        <v>1929.702904300623</v>
-      </c>
-      <c r="E101">
-        <v>7582.313</v>
-      </c>
-      <c r="F101">
-        <v>11066.913</v>
-      </c>
-      <c r="G101">
-        <v>36.1</v>
-      </c>
-      <c r="H101">
-        <v>7694.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>603.8333333333334</v>
-      </c>
-      <c r="K101">
-        <v>6.01</v>
-      </c>
-      <c r="L101">
-        <v>597.8233333333334</v>
-      </c>
-      <c r="M101">
-        <v>2222.2361304</v>
-      </c>
-      <c r="N101">
-        <v>-1624.412797066667</v>
-      </c>
-      <c r="O101">
-        <v>-162.4412797066667</v>
-      </c>
-      <c r="P101">
-        <v>-1461.97151736</v>
-      </c>
-      <c r="Q101">
-        <v>-1455.96151736</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.72926784035911</v>
-      </c>
-      <c r="T101">
-        <v>53.78651695199659</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.02690188162973148</v>
-      </c>
-      <c r="W101">
-        <v>0.1953981021687499</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2690188162973147</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
